--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -1354,57 +1354,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125708132</v>
+        <v>125706524</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495728</v>
+        <v>495786</v>
       </c>
       <c r="R9" t="n">
-        <v>6832782</v>
+        <v>6832670</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1448,19 +1439,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125706524</v>
+        <v>125707173</v>
       </c>
       <c r="B10" t="n">
         <v>78999</v>
@@ -1495,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495786</v>
+        <v>495761</v>
       </c>
       <c r="R10" t="n">
-        <v>6832670</v>
+        <v>6832581</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125707173</v>
+        <v>125707511</v>
       </c>
       <c r="B11" t="n">
-        <v>78999</v>
+        <v>80070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495761</v>
+        <v>495780</v>
       </c>
       <c r="R11" t="n">
-        <v>6832581</v>
+        <v>6832481</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1642,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125707511</v>
+        <v>125706635</v>
       </c>
       <c r="B12" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495780</v>
+        <v>495776</v>
       </c>
       <c r="R12" t="n">
-        <v>6832481</v>
+        <v>6832691</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1739,60 +1730,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125706635</v>
+        <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495776</v>
+        <v>495728</v>
       </c>
       <c r="R13" t="n">
-        <v>6832691</v>
+        <v>6832782</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125708470</v>
+        <v>125706678</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495718</v>
+        <v>495780</v>
       </c>
       <c r="R19" t="n">
-        <v>6832947</v>
+        <v>6832667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2418,69 +2418,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125708060</v>
+        <v>125708470</v>
       </c>
       <c r="B20" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495753</v>
+        <v>495718</v>
       </c>
       <c r="R20" t="n">
-        <v>6832752</v>
+        <v>6832947</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2536,48 +2527,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125706678</v>
+        <v>125708060</v>
       </c>
       <c r="B21" t="n">
-        <v>78726</v>
+        <v>98324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495780</v>
+        <v>495753</v>
       </c>
       <c r="R21" t="n">
-        <v>6832667</v>
+        <v>6832752</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2621,12 +2621,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3515,57 +3515,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125708314</v>
+        <v>125706637</v>
       </c>
       <c r="B31" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495700</v>
+        <v>495737</v>
       </c>
       <c r="R31" t="n">
-        <v>6832875</v>
+        <v>6832680</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3609,19 +3600,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125706637</v>
+        <v>125708848</v>
       </c>
       <c r="B32" t="n">
         <v>80070</v>
@@ -3656,13 +3647,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495737</v>
+        <v>495680</v>
       </c>
       <c r="R32" t="n">
-        <v>6832680</v>
+        <v>6832870</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3706,22 +3697,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125708848</v>
+        <v>125708014</v>
       </c>
       <c r="B33" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3729,21 +3720,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3753,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495680</v>
+        <v>495817</v>
       </c>
       <c r="R33" t="n">
-        <v>6832870</v>
+        <v>6832682</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3815,7 +3806,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125708014</v>
+        <v>125706538</v>
       </c>
       <c r="B34" t="n">
         <v>78967</v>
@@ -3850,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495817</v>
+        <v>495769</v>
       </c>
       <c r="R34" t="n">
-        <v>6832682</v>
+        <v>6832671</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,45 +3903,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125706538</v>
+        <v>125708314</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495769</v>
+        <v>495700</v>
       </c>
       <c r="R35" t="n">
-        <v>6832671</v>
+        <v>6832875</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125707384</v>
+        <v>125706917</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4232,21 +4232,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495765</v>
+        <v>495776</v>
       </c>
       <c r="R38" t="n">
-        <v>6832558</v>
+        <v>6832649</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4306,19 +4306,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B39" t="n">
         <v>78999</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R39" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,10 +4415,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125706947</v>
+        <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4426,21 +4426,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4450,13 +4450,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495763</v>
+        <v>495765</v>
       </c>
       <c r="R40" t="n">
-        <v>6832629</v>
+        <v>6832558</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4500,12 +4500,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4909,48 +4909,63 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125706720</v>
+        <v>125707718</v>
       </c>
       <c r="B45" t="n">
-        <v>78999</v>
+        <v>56843</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495782</v>
+        <v>495818</v>
       </c>
       <c r="R45" t="n">
-        <v>6832661</v>
+        <v>6832436</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4994,60 +5009,54 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125707718</v>
+        <v>125708266</v>
       </c>
       <c r="B46" t="n">
-        <v>56843</v>
+        <v>98324</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5056,13 +5065,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495818</v>
+        <v>495706</v>
       </c>
       <c r="R46" t="n">
-        <v>6832436</v>
+        <v>6832880</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5106,66 +5115,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B47" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R47" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6009,45 +6009,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125707134</v>
+        <v>125706779</v>
       </c>
       <c r="B56" t="n">
-        <v>56958</v>
+        <v>98324</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495770</v>
+        <v>495724</v>
       </c>
       <c r="R56" t="n">
-        <v>6832555</v>
+        <v>6832662</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6106,54 +6115,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125707479</v>
+        <v>125707134</v>
       </c>
       <c r="B57" t="n">
-        <v>98324</v>
+        <v>56958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495776</v>
+        <v>495770</v>
       </c>
       <c r="R57" t="n">
-        <v>6832485</v>
+        <v>6832555</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125706779</v>
+        <v>125707479</v>
       </c>
       <c r="B58" t="n">
         <v>98324</v>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495724</v>
+        <v>495776</v>
       </c>
       <c r="R58" t="n">
-        <v>6832662</v>
+        <v>6832485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125706872</v>
+        <v>125707417</v>
       </c>
       <c r="B4" t="n">
-        <v>78999</v>
+        <v>79585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495765</v>
+        <v>495819</v>
       </c>
       <c r="R4" t="n">
-        <v>6832663</v>
+        <v>6832571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706791</v>
+        <v>125706872</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495730</v>
+        <v>495765</v>
       </c>
       <c r="R5" t="n">
-        <v>6832652</v>
+        <v>6832663</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125707417</v>
+        <v>125706791</v>
       </c>
       <c r="B6" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495819</v>
+        <v>495730</v>
       </c>
       <c r="R6" t="n">
-        <v>6832571</v>
+        <v>6832652</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,12 +1148,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
         <v>125706913</v>
       </c>
       <c r="B8" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125706524</v>
+        <v>125707511</v>
       </c>
       <c r="B9" t="n">
-        <v>78999</v>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495786</v>
+        <v>495780</v>
       </c>
       <c r="R9" t="n">
-        <v>6832670</v>
+        <v>6832481</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,60 +1439,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125707173</v>
+        <v>125708132</v>
       </c>
       <c r="B10" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495761</v>
+        <v>495728</v>
       </c>
       <c r="R10" t="n">
-        <v>6832581</v>
+        <v>6832782</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1545,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125707511</v>
+        <v>125706635</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,13 +1592,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495780</v>
+        <v>495776</v>
       </c>
       <c r="R11" t="n">
-        <v>6832481</v>
+        <v>6832691</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1642,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125706635</v>
+        <v>125707173</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495776</v>
+        <v>495761</v>
       </c>
       <c r="R12" t="n">
-        <v>6832691</v>
+        <v>6832581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,57 +1751,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125708132</v>
+        <v>125706524</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495728</v>
+        <v>495786</v>
       </c>
       <c r="R13" t="n">
-        <v>6832782</v>
+        <v>6832670</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>125707583</v>
       </c>
       <c r="B14" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125707544</v>
+        <v>125708856</v>
       </c>
       <c r="B15" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,37 +1956,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495877</v>
+        <v>495902</v>
       </c>
       <c r="R15" t="n">
-        <v>6832537</v>
+        <v>6833046</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2030,12 +2030,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125708856</v>
+        <v>125707048</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2170,17 +2170,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495902</v>
+        <v>495746</v>
       </c>
       <c r="R17" t="n">
-        <v>6833046</v>
+        <v>6832627</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2224,22 +2224,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125707048</v>
+        <v>125707544</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495746</v>
+        <v>495877</v>
       </c>
       <c r="R18" t="n">
-        <v>6832627</v>
+        <v>6832537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,48 +2333,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125706678</v>
+        <v>125708060</v>
       </c>
       <c r="B19" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495780</v>
+        <v>495753</v>
       </c>
       <c r="R19" t="n">
-        <v>6832667</v>
+        <v>6832752</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2418,22 +2427,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125708470</v>
+        <v>125706678</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2450,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495718</v>
+        <v>495780</v>
       </c>
       <c r="R20" t="n">
-        <v>6832947</v>
+        <v>6832667</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2515,69 +2524,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125708060</v>
+        <v>125708470</v>
       </c>
       <c r="B21" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495753</v>
+        <v>495718</v>
       </c>
       <c r="R21" t="n">
-        <v>6832752</v>
+        <v>6832947</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125706788</v>
+        <v>125707543</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495756</v>
+        <v>495772</v>
       </c>
       <c r="R23" t="n">
-        <v>6832675</v>
+        <v>6832482</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2815,22 +2815,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125707543</v>
+        <v>125706777</v>
       </c>
       <c r="B24" t="n">
-        <v>80070</v>
+        <v>78999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495772</v>
+        <v>495767</v>
       </c>
       <c r="R24" t="n">
-        <v>6832482</v>
+        <v>6832677</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2912,60 +2912,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125706777</v>
+        <v>125707033</v>
       </c>
       <c r="B25" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495767</v>
+        <v>495733</v>
       </c>
       <c r="R25" t="n">
-        <v>6832677</v>
+        <v>6832598</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3009,69 +3018,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125707033</v>
+        <v>125706788</v>
       </c>
       <c r="B26" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495733</v>
+        <v>495756</v>
       </c>
       <c r="R26" t="n">
-        <v>6832598</v>
+        <v>6832675</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3115,44 +3115,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125706487</v>
+        <v>125706444</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495759</v>
+        <v>495750</v>
       </c>
       <c r="R27" t="n">
-        <v>6832688</v>
+        <v>6832709</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3224,32 +3224,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125706444</v>
+        <v>125706487</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495750</v>
+        <v>495759</v>
       </c>
       <c r="R28" t="n">
-        <v>6832709</v>
+        <v>6832688</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125707016</v>
+        <v>125708848</v>
       </c>
       <c r="B29" t="n">
-        <v>78999</v>
+        <v>80070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495749</v>
+        <v>495680</v>
       </c>
       <c r="R29" t="n">
-        <v>6832629</v>
+        <v>6832870</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125707083</v>
+        <v>125707016</v>
       </c>
       <c r="B30" t="n">
         <v>78999</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495751</v>
+        <v>495749</v>
       </c>
       <c r="R30" t="n">
-        <v>6832612</v>
+        <v>6832629</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125706637</v>
+        <v>125707083</v>
       </c>
       <c r="B31" t="n">
-        <v>80070</v>
+        <v>78999</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,21 +3526,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3550,13 +3550,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495737</v>
+        <v>495751</v>
       </c>
       <c r="R31" t="n">
-        <v>6832680</v>
+        <v>6832612</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3600,57 +3600,66 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125708848</v>
+        <v>125706445</v>
       </c>
       <c r="B32" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495680</v>
+        <v>495778</v>
       </c>
       <c r="R32" t="n">
-        <v>6832870</v>
+        <v>6832690</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,45 +3718,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125708014</v>
+        <v>125708314</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495817</v>
+        <v>495700</v>
       </c>
       <c r="R33" t="n">
-        <v>6832682</v>
+        <v>6832875</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125706538</v>
+        <v>125706637</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3817,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3841,13 +3859,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495769</v>
+        <v>495737</v>
       </c>
       <c r="R34" t="n">
-        <v>6832671</v>
+        <v>6832680</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3891,66 +3909,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125708314</v>
+        <v>125708014</v>
       </c>
       <c r="B35" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495700</v>
+        <v>495817</v>
       </c>
       <c r="R35" t="n">
-        <v>6832875</v>
+        <v>6832682</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,54 +4018,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125706445</v>
+        <v>125706538</v>
       </c>
       <c r="B36" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495778</v>
+        <v>495769</v>
       </c>
       <c r="R36" t="n">
-        <v>6832690</v>
+        <v>6832671</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,57 +4115,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125707003</v>
+        <v>125706947</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495724</v>
+        <v>495763</v>
       </c>
       <c r="R37" t="n">
-        <v>6832599</v>
+        <v>6832629</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4209,12 +4200,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4318,10 +4309,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706947</v>
+        <v>125707384</v>
       </c>
       <c r="B39" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4329,21 +4320,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4353,13 +4344,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495763</v>
+        <v>495765</v>
       </c>
       <c r="R39" t="n">
-        <v>6832629</v>
+        <v>6832558</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4403,57 +4394,66 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707384</v>
+        <v>125707003</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495765</v>
+        <v>495724</v>
       </c>
       <c r="R40" t="n">
-        <v>6832558</v>
+        <v>6832599</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4512,10 +4512,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125707372</v>
+        <v>125706892</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495764</v>
+        <v>495711</v>
       </c>
       <c r="R41" t="n">
-        <v>6832553</v>
+        <v>6832636</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4609,32 +4609,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125706892</v>
+        <v>125706691</v>
       </c>
       <c r="B42" t="n">
-        <v>80070</v>
+        <v>78991</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495711</v>
+        <v>495777</v>
       </c>
       <c r="R42" t="n">
-        <v>6832636</v>
+        <v>6832671</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4694,57 +4694,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125706691</v>
+        <v>125706714</v>
       </c>
       <c r="B43" t="n">
-        <v>78991</v>
+        <v>98331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495777</v>
+        <v>495751</v>
       </c>
       <c r="R43" t="n">
-        <v>6832671</v>
+        <v>6832672</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4791,69 +4800,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125706714</v>
+        <v>125707372</v>
       </c>
       <c r="B44" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495751</v>
+        <v>495764</v>
       </c>
       <c r="R44" t="n">
-        <v>6832672</v>
+        <v>6832553</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5021,54 +5021,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B46" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R46" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5127,45 +5118,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125706720</v>
+        <v>125708266</v>
       </c>
       <c r="B47" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495782</v>
+        <v>495706</v>
       </c>
       <c r="R47" t="n">
-        <v>6832661</v>
+        <v>6832880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5224,54 +5224,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125707720</v>
+        <v>125706842</v>
       </c>
       <c r="B48" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495839</v>
+        <v>495760</v>
       </c>
       <c r="R48" t="n">
-        <v>6832437</v>
+        <v>6832666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5330,45 +5321,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125706842</v>
+        <v>125707720</v>
       </c>
       <c r="B49" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495760</v>
+        <v>495839</v>
       </c>
       <c r="R49" t="n">
-        <v>6832666</v>
+        <v>6832437</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125706764</v>
+        <v>125708210</v>
       </c>
       <c r="B52" t="n">
-        <v>78999</v>
+        <v>80070</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495761</v>
+        <v>495705</v>
       </c>
       <c r="R52" t="n">
-        <v>6832671</v>
+        <v>6832884</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5718,7 +5718,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125708210</v>
+        <v>125706943</v>
       </c>
       <c r="B53" t="n">
         <v>80070</v>
@@ -5753,13 +5753,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495705</v>
+        <v>495715</v>
       </c>
       <c r="R53" t="n">
-        <v>6832884</v>
+        <v>6832599</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5803,19 +5803,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706943</v>
+        <v>125708307</v>
       </c>
       <c r="B54" t="n">
         <v>80070</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495715</v>
+        <v>495712</v>
       </c>
       <c r="R54" t="n">
-        <v>6832599</v>
+        <v>6832874</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5912,45 +5912,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708307</v>
+        <v>125706779</v>
       </c>
       <c r="B55" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495712</v>
+        <v>495724</v>
       </c>
       <c r="R55" t="n">
-        <v>6832874</v>
+        <v>6832662</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6009,10 +6018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706779</v>
+        <v>125707479</v>
       </c>
       <c r="B56" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,7 +6048,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6053,10 +6062,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495724</v>
+        <v>495776</v>
       </c>
       <c r="R56" t="n">
-        <v>6832662</v>
+        <v>6832485</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6212,57 +6221,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125707479</v>
+        <v>125706764</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495776</v>
+        <v>495761</v>
       </c>
       <c r="R58" t="n">
-        <v>6832485</v>
+        <v>6832671</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6306,66 +6306,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125707493</v>
+        <v>125707093</v>
       </c>
       <c r="B59" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495766</v>
+        <v>495727</v>
       </c>
       <c r="R59" t="n">
-        <v>6832499</v>
+        <v>6832581</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6521,45 +6512,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125707093</v>
+        <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495727</v>
+        <v>495766</v>
       </c>
       <c r="R61" t="n">
-        <v>6832581</v>
+        <v>6832499</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125707370</v>
+        <v>125706395</v>
       </c>
       <c r="B62" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495793</v>
+        <v>495818</v>
       </c>
       <c r="R62" t="n">
-        <v>6832568</v>
+        <v>6832725</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,60 +6703,69 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125706395</v>
+        <v>125707073</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495818</v>
+        <v>495738</v>
       </c>
       <c r="R63" t="n">
-        <v>6832725</v>
+        <v>6832601</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6812,57 +6821,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707073</v>
+        <v>125707370</v>
       </c>
       <c r="B64" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495738</v>
+        <v>495793</v>
       </c>
       <c r="R64" t="n">
-        <v>6832601</v>
+        <v>6832568</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6906,22 +6906,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708583</v>
+        <v>125708596</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,37 +6929,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495841</v>
+        <v>495930</v>
       </c>
       <c r="R65" t="n">
-        <v>6833181</v>
+        <v>6833128</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7003,12 +7003,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125708596</v>
+        <v>125706873</v>
       </c>
       <c r="B67" t="n">
         <v>80070</v>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495930</v>
+        <v>495718</v>
       </c>
       <c r="R67" t="n">
-        <v>6833128</v>
+        <v>6832621</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7197,22 +7197,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125706873</v>
+        <v>125708583</v>
       </c>
       <c r="B68" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,34 +7220,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495718</v>
+        <v>495841</v>
       </c>
       <c r="R68" t="n">
-        <v>6832621</v>
+        <v>6833181</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -1354,45 +1354,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125707511</v>
+        <v>125708132</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495780</v>
+        <v>495728</v>
       </c>
       <c r="R9" t="n">
-        <v>6832481</v>
+        <v>6832782</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1451,54 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125708132</v>
+        <v>125707511</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495728</v>
+        <v>495780</v>
       </c>
       <c r="R10" t="n">
-        <v>6832782</v>
+        <v>6832481</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2333,57 +2333,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125708060</v>
+        <v>125708470</v>
       </c>
       <c r="B19" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495753</v>
+        <v>495718</v>
       </c>
       <c r="R19" t="n">
-        <v>6832752</v>
+        <v>6832947</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2439,48 +2430,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125706678</v>
+        <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495780</v>
+        <v>495753</v>
       </c>
       <c r="R20" t="n">
-        <v>6832667</v>
+        <v>6832752</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2524,22 +2524,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125708470</v>
+        <v>125706678</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495718</v>
+        <v>495780</v>
       </c>
       <c r="R21" t="n">
-        <v>6832947</v>
+        <v>6832667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,12 +2621,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4115,48 +4115,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125706947</v>
+        <v>125707003</v>
       </c>
       <c r="B37" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495763</v>
+        <v>495724</v>
       </c>
       <c r="R37" t="n">
-        <v>6832629</v>
+        <v>6832599</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4200,19 +4209,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B38" t="n">
         <v>78999</v>
@@ -4247,10 +4256,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R38" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,10 +4318,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125707384</v>
+        <v>125706917</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4320,21 +4329,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,13 +4353,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495765</v>
+        <v>495776</v>
       </c>
       <c r="R39" t="n">
-        <v>6832558</v>
+        <v>6832649</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4394,66 +4403,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707003</v>
+        <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495724</v>
+        <v>495765</v>
       </c>
       <c r="R40" t="n">
-        <v>6832599</v>
+        <v>6832558</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4512,48 +4512,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125706892</v>
+        <v>125706714</v>
       </c>
       <c r="B41" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495711</v>
+        <v>495751</v>
       </c>
       <c r="R41" t="n">
-        <v>6832636</v>
+        <v>6832672</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4609,32 +4618,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125706691</v>
+        <v>125706892</v>
       </c>
       <c r="B42" t="n">
-        <v>78991</v>
+        <v>80070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,13 +4653,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495777</v>
+        <v>495711</v>
       </c>
       <c r="R42" t="n">
-        <v>6832671</v>
+        <v>6832636</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4694,66 +4703,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125706714</v>
+        <v>125706691</v>
       </c>
       <c r="B43" t="n">
-        <v>98331</v>
+        <v>78991</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495751</v>
+        <v>495777</v>
       </c>
       <c r="R43" t="n">
-        <v>6832672</v>
+        <v>6832671</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4800,12 +4800,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4909,63 +4909,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125707718</v>
+        <v>125706720</v>
       </c>
       <c r="B45" t="n">
-        <v>56843</v>
+        <v>78999</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495818</v>
+        <v>495782</v>
       </c>
       <c r="R45" t="n">
-        <v>6832436</v>
+        <v>6832661</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5009,60 +4994,75 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125706720</v>
+        <v>125707718</v>
       </c>
       <c r="B46" t="n">
-        <v>78999</v>
+        <v>56843</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495782</v>
+        <v>495818</v>
       </c>
       <c r="R46" t="n">
-        <v>6832661</v>
+        <v>6832436</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5106,12 +5106,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125706842</v>
+        <v>125706827</v>
       </c>
       <c r="B48" t="n">
-        <v>78999</v>
+        <v>78725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495760</v>
+        <v>495745</v>
       </c>
       <c r="R48" t="n">
-        <v>6832666</v>
+        <v>6832669</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,54 +5321,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125707720</v>
+        <v>125707108</v>
       </c>
       <c r="B49" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495839</v>
+        <v>495743</v>
       </c>
       <c r="R49" t="n">
-        <v>6832437</v>
+        <v>6832597</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,10 +5418,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125706827</v>
+        <v>125706842</v>
       </c>
       <c r="B50" t="n">
-        <v>78725</v>
+        <v>78999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5438,21 +5429,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5462,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495745</v>
+        <v>495760</v>
       </c>
       <c r="R50" t="n">
-        <v>6832669</v>
+        <v>6832666</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5524,45 +5515,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125707108</v>
+        <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495743</v>
+        <v>495839</v>
       </c>
       <c r="R51" t="n">
-        <v>6832597</v>
+        <v>6832437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125707093</v>
+        <v>125707413</v>
       </c>
       <c r="B59" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495727</v>
+        <v>495782</v>
       </c>
       <c r="R59" t="n">
-        <v>6832581</v>
+        <v>6832513</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6415,45 +6415,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707413</v>
+        <v>125707493</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495782</v>
+        <v>495766</v>
       </c>
       <c r="R60" t="n">
-        <v>6832513</v>
+        <v>6832499</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6512,54 +6521,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125707493</v>
+        <v>125707093</v>
       </c>
       <c r="B61" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495766</v>
+        <v>495727</v>
       </c>
       <c r="R61" t="n">
-        <v>6832499</v>
+        <v>6832581</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R62" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,69 +6703,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B63" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R63" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6821,48 +6812,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707370</v>
+        <v>125707073</v>
       </c>
       <c r="B64" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495793</v>
+        <v>495738</v>
       </c>
       <c r="R64" t="n">
-        <v>6832568</v>
+        <v>6832601</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6906,12 +6906,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -1354,54 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125708132</v>
+        <v>125707511</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495728</v>
+        <v>495780</v>
       </c>
       <c r="R9" t="n">
-        <v>6832782</v>
+        <v>6832481</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,45 +1451,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125707511</v>
+        <v>125708132</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495780</v>
+        <v>495728</v>
       </c>
       <c r="R10" t="n">
-        <v>6832481</v>
+        <v>6832782</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125707543</v>
+        <v>125706788</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495772</v>
+        <v>495756</v>
       </c>
       <c r="R23" t="n">
-        <v>6832482</v>
+        <v>6832675</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2815,12 +2815,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125706788</v>
+        <v>125707543</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3041,21 +3041,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495756</v>
+        <v>495772</v>
       </c>
       <c r="R26" t="n">
-        <v>6832675</v>
+        <v>6832482</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3115,12 +3115,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3321,45 +3321,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125708848</v>
+        <v>125706445</v>
       </c>
       <c r="B29" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495680</v>
+        <v>495778</v>
       </c>
       <c r="R29" t="n">
-        <v>6832870</v>
+        <v>6832690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,45 +3427,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125707016</v>
+        <v>125708314</v>
       </c>
       <c r="B30" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495749</v>
+        <v>495700</v>
       </c>
       <c r="R30" t="n">
-        <v>6832629</v>
+        <v>6832875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,10 +3533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125707083</v>
+        <v>125708848</v>
       </c>
       <c r="B31" t="n">
-        <v>78999</v>
+        <v>80070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,21 +3544,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3550,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495751</v>
+        <v>495680</v>
       </c>
       <c r="R31" t="n">
-        <v>6832612</v>
+        <v>6832870</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3612,54 +3630,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125706445</v>
+        <v>125708014</v>
       </c>
       <c r="B32" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495778</v>
+        <v>495817</v>
       </c>
       <c r="R32" t="n">
-        <v>6832690</v>
+        <v>6832682</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3718,54 +3727,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125708314</v>
+        <v>125706538</v>
       </c>
       <c r="B33" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495700</v>
+        <v>495769</v>
       </c>
       <c r="R33" t="n">
-        <v>6832875</v>
+        <v>6832671</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125708014</v>
+        <v>125707016</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3932,21 +3932,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495817</v>
+        <v>495749</v>
       </c>
       <c r="R35" t="n">
-        <v>6832682</v>
+        <v>6832629</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,10 +4018,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125706538</v>
+        <v>125707083</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4029,21 +4029,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495769</v>
+        <v>495751</v>
       </c>
       <c r="R36" t="n">
-        <v>6832671</v>
+        <v>6832612</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4512,57 +4512,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125706714</v>
+        <v>125707372</v>
       </c>
       <c r="B41" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495751</v>
+        <v>495764</v>
       </c>
       <c r="R41" t="n">
-        <v>6832672</v>
+        <v>6832553</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4812,48 +4803,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125707372</v>
+        <v>125706714</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495764</v>
+        <v>495751</v>
       </c>
       <c r="R44" t="n">
-        <v>6832553</v>
+        <v>6832672</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5006,48 +5006,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125707718</v>
+        <v>125708266</v>
       </c>
       <c r="B46" t="n">
-        <v>56843</v>
+        <v>98331</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5056,13 +5050,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495818</v>
+        <v>495706</v>
       </c>
       <c r="R46" t="n">
-        <v>6832436</v>
+        <v>6832880</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5106,54 +5100,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708266</v>
+        <v>125707718</v>
       </c>
       <c r="B47" t="n">
-        <v>98331</v>
+        <v>56843</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495706</v>
+        <v>495818</v>
       </c>
       <c r="R47" t="n">
-        <v>6832880</v>
+        <v>6832436</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5212,12 +5212,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708596</v>
+        <v>125708583</v>
       </c>
       <c r="B65" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,37 +6929,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495930</v>
+        <v>495841</v>
       </c>
       <c r="R65" t="n">
-        <v>6833128</v>
+        <v>6833181</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7003,12 +7003,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125706873</v>
+        <v>125708596</v>
       </c>
       <c r="B67" t="n">
         <v>80070</v>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495718</v>
+        <v>495930</v>
       </c>
       <c r="R67" t="n">
-        <v>6832621</v>
+        <v>6833128</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7197,22 +7197,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125708583</v>
+        <v>125706873</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,34 +7220,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495841</v>
+        <v>495718</v>
       </c>
       <c r="R68" t="n">
-        <v>6833181</v>
+        <v>6832621</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125708078</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707087</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707417</v>
+        <v>125706872</v>
       </c>
       <c r="B4" t="n">
-        <v>79585</v>
+        <v>79000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495819</v>
+        <v>495765</v>
       </c>
       <c r="R4" t="n">
-        <v>6832571</v>
+        <v>6832663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706872</v>
+        <v>125706791</v>
       </c>
       <c r="B5" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495765</v>
+        <v>495730</v>
       </c>
       <c r="R5" t="n">
-        <v>6832663</v>
+        <v>6832652</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125706791</v>
+        <v>125707417</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495730</v>
+        <v>495819</v>
       </c>
       <c r="R6" t="n">
-        <v>6832652</v>
+        <v>6832571</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125708227</v>
+        <v>125706913</v>
       </c>
       <c r="B7" t="n">
-        <v>80071</v>
+        <v>92518</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495692</v>
+        <v>495727</v>
       </c>
       <c r="R7" t="n">
-        <v>6832878</v>
+        <v>6832609</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125706913</v>
+        <v>125708227</v>
       </c>
       <c r="B8" t="n">
-        <v>92509</v>
+        <v>80072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495727</v>
+        <v>495692</v>
       </c>
       <c r="R8" t="n">
-        <v>6832609</v>
+        <v>6832878</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125707511</v>
+        <v>125707173</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>79000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495780</v>
+        <v>495761</v>
       </c>
       <c r="R9" t="n">
-        <v>6832481</v>
+        <v>6832581</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,66 +1439,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125708132</v>
+        <v>125707511</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495728</v>
+        <v>495780</v>
       </c>
       <c r="R10" t="n">
-        <v>6832782</v>
+        <v>6832481</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1551,7 @@
         <v>125706635</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125707173</v>
+        <v>125706524</v>
       </c>
       <c r="B12" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1689,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495761</v>
+        <v>495786</v>
       </c>
       <c r="R12" t="n">
-        <v>6832581</v>
+        <v>6832670</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,48 +1742,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125706524</v>
+        <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>78999</v>
+        <v>98334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495786</v>
+        <v>495728</v>
       </c>
       <c r="R13" t="n">
-        <v>6832670</v>
+        <v>6832782</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>125707583</v>
       </c>
       <c r="B14" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125708856</v>
+        <v>125707544</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,37 +1956,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495902</v>
+        <v>495877</v>
       </c>
       <c r="R15" t="n">
-        <v>6833046</v>
+        <v>6832537</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2030,22 +2030,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125707655</v>
+        <v>125708856</v>
       </c>
       <c r="B16" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,34 +2053,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495798</v>
+        <v>495902</v>
       </c>
       <c r="R16" t="n">
-        <v>6832444</v>
+        <v>6833046</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2142,7 +2142,7 @@
         <v>125707048</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125707544</v>
+        <v>125707655</v>
       </c>
       <c r="B18" t="n">
-        <v>78999</v>
+        <v>80071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495877</v>
+        <v>495798</v>
       </c>
       <c r="R18" t="n">
-        <v>6832537</v>
+        <v>6832444</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2321,22 +2321,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125708470</v>
+        <v>125706678</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495718</v>
+        <v>495780</v>
       </c>
       <c r="R19" t="n">
-        <v>6832947</v>
+        <v>6832667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2418,12 +2418,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
         <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125706678</v>
+        <v>125708470</v>
       </c>
       <c r="B21" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495780</v>
+        <v>495718</v>
       </c>
       <c r="R21" t="n">
-        <v>6832667</v>
+        <v>6832947</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,12 +2621,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
         <v>125706549</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>125706788</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,48 +2827,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125706777</v>
+        <v>125707033</v>
       </c>
       <c r="B24" t="n">
-        <v>78999</v>
+        <v>98334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495767</v>
+        <v>495733</v>
       </c>
       <c r="R24" t="n">
-        <v>6832677</v>
+        <v>6832598</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2912,69 +2921,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125707033</v>
+        <v>125706777</v>
       </c>
       <c r="B25" t="n">
-        <v>98331</v>
+        <v>79000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495733</v>
+        <v>495767</v>
       </c>
       <c r="R25" t="n">
-        <v>6832598</v>
+        <v>6832677</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3018,12 +3018,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
         <v>125707543</v>
       </c>
       <c r="B26" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>125706444</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125706487</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,54 +3321,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125706445</v>
+        <v>125708014</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495778</v>
+        <v>495817</v>
       </c>
       <c r="R29" t="n">
-        <v>6832690</v>
+        <v>6832682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,54 +3418,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125708314</v>
+        <v>125706538</v>
       </c>
       <c r="B30" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495700</v>
+        <v>495769</v>
       </c>
       <c r="R30" t="n">
-        <v>6832875</v>
+        <v>6832671</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125708848</v>
+        <v>125707016</v>
       </c>
       <c r="B31" t="n">
-        <v>80070</v>
+        <v>79000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,21 +3526,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3550,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495680</v>
+        <v>495749</v>
       </c>
       <c r="R31" t="n">
-        <v>6832870</v>
+        <v>6832629</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,10 +3612,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125708014</v>
+        <v>125707083</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,21 +3623,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495817</v>
+        <v>495751</v>
       </c>
       <c r="R32" t="n">
-        <v>6832682</v>
+        <v>6832612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,10 +3709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125706538</v>
+        <v>125706637</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3720,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,13 +3744,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495769</v>
+        <v>495737</v>
       </c>
       <c r="R33" t="n">
-        <v>6832671</v>
+        <v>6832680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3812,22 +3794,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125706637</v>
+        <v>125708848</v>
       </c>
       <c r="B34" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,13 +3841,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495737</v>
+        <v>495680</v>
       </c>
       <c r="R34" t="n">
-        <v>6832680</v>
+        <v>6832870</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3909,57 +3891,66 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125707016</v>
+        <v>125708314</v>
       </c>
       <c r="B35" t="n">
-        <v>78999</v>
+        <v>98334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495749</v>
+        <v>495700</v>
       </c>
       <c r="R35" t="n">
-        <v>6832629</v>
+        <v>6832875</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,45 +4009,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125707083</v>
+        <v>125706445</v>
       </c>
       <c r="B36" t="n">
-        <v>78999</v>
+        <v>98334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495751</v>
+        <v>495778</v>
       </c>
       <c r="R36" t="n">
-        <v>6832612</v>
+        <v>6832690</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4118,7 +4118,7 @@
         <v>125707003</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706947</v>
+        <v>125706917</v>
       </c>
       <c r="B38" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495763</v>
+        <v>495776</v>
       </c>
       <c r="R38" t="n">
-        <v>6832629</v>
+        <v>6832649</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,10 +4318,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B39" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R39" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4418,7 +4418,7 @@
         <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125707372</v>
+        <v>125706892</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4523,21 +4523,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495764</v>
+        <v>495711</v>
       </c>
       <c r="R41" t="n">
-        <v>6832553</v>
+        <v>6832636</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4609,32 +4609,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125706892</v>
+        <v>125706691</v>
       </c>
       <c r="B42" t="n">
-        <v>80070</v>
+        <v>78992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495711</v>
+        <v>495777</v>
       </c>
       <c r="R42" t="n">
-        <v>6832636</v>
+        <v>6832671</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4694,44 +4694,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125706691</v>
+        <v>125707372</v>
       </c>
       <c r="B43" t="n">
-        <v>78991</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495777</v>
+        <v>495764</v>
       </c>
       <c r="R43" t="n">
-        <v>6832671</v>
+        <v>6832553</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4791,12 +4791,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
         <v>125706714</v>
       </c>
       <c r="B44" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,45 +4909,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125706720</v>
+        <v>125708266</v>
       </c>
       <c r="B45" t="n">
-        <v>78999</v>
+        <v>98334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495782</v>
+        <v>495706</v>
       </c>
       <c r="R45" t="n">
-        <v>6832661</v>
+        <v>6832880</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5006,54 +5015,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B46" t="n">
-        <v>98331</v>
+        <v>79000</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R46" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125706827</v>
+        <v>125706842</v>
       </c>
       <c r="B48" t="n">
-        <v>78725</v>
+        <v>79000</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495745</v>
+        <v>495760</v>
       </c>
       <c r="R48" t="n">
-        <v>6832669</v>
+        <v>6832666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5324,7 +5324,7 @@
         <v>125707108</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5418,10 +5418,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125706842</v>
+        <v>125706827</v>
       </c>
       <c r="B50" t="n">
-        <v>78999</v>
+        <v>78726</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,21 +5429,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495760</v>
+        <v>495745</v>
       </c>
       <c r="R50" t="n">
-        <v>6832666</v>
+        <v>6832669</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>125708210</v>
       </c>
       <c r="B52" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5718,10 +5718,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125706943</v>
+        <v>125706764</v>
       </c>
       <c r="B53" t="n">
-        <v>80070</v>
+        <v>79000</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5729,21 +5729,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5753,13 +5753,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495715</v>
+        <v>495761</v>
       </c>
       <c r="R53" t="n">
-        <v>6832599</v>
+        <v>6832671</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5803,22 +5803,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125708307</v>
+        <v>125706943</v>
       </c>
       <c r="B54" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495712</v>
+        <v>495715</v>
       </c>
       <c r="R54" t="n">
-        <v>6832874</v>
+        <v>6832599</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5912,54 +5912,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125706779</v>
+        <v>125708307</v>
       </c>
       <c r="B55" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495724</v>
+        <v>495712</v>
       </c>
       <c r="R55" t="n">
-        <v>6832662</v>
+        <v>6832874</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6018,54 +6009,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125707479</v>
+        <v>125707134</v>
       </c>
       <c r="B56" t="n">
-        <v>98331</v>
+        <v>56958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495776</v>
+        <v>495770</v>
       </c>
       <c r="R56" t="n">
-        <v>6832485</v>
+        <v>6832555</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6124,45 +6106,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125707134</v>
+        <v>125707479</v>
       </c>
       <c r="B57" t="n">
-        <v>56958</v>
+        <v>98334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495770</v>
+        <v>495776</v>
       </c>
       <c r="R57" t="n">
-        <v>6832555</v>
+        <v>6832485</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6221,48 +6212,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125706764</v>
+        <v>125706779</v>
       </c>
       <c r="B58" t="n">
-        <v>78999</v>
+        <v>98334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495761</v>
+        <v>495724</v>
       </c>
       <c r="R58" t="n">
-        <v>6832671</v>
+        <v>6832662</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6306,22 +6306,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125707413</v>
+        <v>125707093</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495782</v>
+        <v>495727</v>
       </c>
       <c r="R59" t="n">
-        <v>6832513</v>
+        <v>6832581</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6415,54 +6415,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707493</v>
+        <v>125707413</v>
       </c>
       <c r="B60" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495766</v>
+        <v>495782</v>
       </c>
       <c r="R60" t="n">
-        <v>6832499</v>
+        <v>6832513</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6521,45 +6512,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125707093</v>
+        <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495727</v>
+        <v>495766</v>
       </c>
       <c r="R61" t="n">
-        <v>6832581</v>
+        <v>6832499</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6621,7 +6621,7 @@
         <v>125707370</v>
       </c>
       <c r="B62" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>125706395</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>125707073</v>
       </c>
       <c r="B64" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708583</v>
+        <v>125708074</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,34 +6929,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495841</v>
+        <v>495733</v>
       </c>
       <c r="R65" t="n">
-        <v>6833181</v>
+        <v>6832780</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125708074</v>
+        <v>125708596</v>
       </c>
       <c r="B66" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7050,13 +7050,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495733</v>
+        <v>495930</v>
       </c>
       <c r="R66" t="n">
-        <v>6832780</v>
+        <v>6833128</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7100,22 +7100,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125708596</v>
+        <v>125706873</v>
       </c>
       <c r="B67" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495930</v>
+        <v>495718</v>
       </c>
       <c r="R67" t="n">
-        <v>6833128</v>
+        <v>6832621</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7197,22 +7197,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125706873</v>
+        <v>125708583</v>
       </c>
       <c r="B68" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,34 +7220,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495718</v>
+        <v>495841</v>
       </c>
       <c r="R68" t="n">
-        <v>6832621</v>
+        <v>6833181</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125706678</v>
+        <v>125708470</v>
       </c>
       <c r="B19" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495780</v>
+        <v>495718</v>
       </c>
       <c r="R19" t="n">
-        <v>6832667</v>
+        <v>6832947</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2418,69 +2418,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125708060</v>
+        <v>125706678</v>
       </c>
       <c r="B20" t="n">
-        <v>98334</v>
+        <v>78727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495753</v>
+        <v>495780</v>
       </c>
       <c r="R20" t="n">
-        <v>6832752</v>
+        <v>6832667</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2524,60 +2515,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125708470</v>
+        <v>125708060</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495718</v>
+        <v>495753</v>
       </c>
       <c r="R21" t="n">
-        <v>6832947</v>
+        <v>6832752</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4909,54 +4909,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B45" t="n">
-        <v>98334</v>
+        <v>79000</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R45" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5015,48 +5006,63 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125706720</v>
+        <v>125707718</v>
       </c>
       <c r="B46" t="n">
-        <v>79000</v>
+        <v>56843</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495782</v>
+        <v>495818</v>
       </c>
       <c r="R46" t="n">
-        <v>6832661</v>
+        <v>6832436</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5100,60 +5106,54 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125707718</v>
+        <v>125708266</v>
       </c>
       <c r="B47" t="n">
-        <v>56843</v>
+        <v>98334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495818</v>
+        <v>495706</v>
       </c>
       <c r="R47" t="n">
-        <v>6832436</v>
+        <v>6832880</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5212,12 +5212,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125708210</v>
+        <v>125706764</v>
       </c>
       <c r="B52" t="n">
-        <v>80071</v>
+        <v>79000</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495705</v>
+        <v>495761</v>
       </c>
       <c r="R52" t="n">
-        <v>6832884</v>
+        <v>6832671</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5718,10 +5718,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125706764</v>
+        <v>125708210</v>
       </c>
       <c r="B53" t="n">
-        <v>79000</v>
+        <v>80071</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5729,21 +5729,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495761</v>
+        <v>495705</v>
       </c>
       <c r="R53" t="n">
-        <v>6832671</v>
+        <v>6832884</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125707370</v>
+        <v>125706395</v>
       </c>
       <c r="B62" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495793</v>
+        <v>495818</v>
       </c>
       <c r="R62" t="n">
-        <v>6832568</v>
+        <v>6832725</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,22 +6703,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B63" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R63" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6800,12 +6800,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125708078</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707087</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125706872</v>
+        <v>125706913</v>
       </c>
       <c r="B4" t="n">
-        <v>79000</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495765</v>
+        <v>495727</v>
       </c>
       <c r="R4" t="n">
-        <v>6832663</v>
+        <v>6832609</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706791</v>
+        <v>125706872</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495730</v>
+        <v>495765</v>
       </c>
       <c r="R5" t="n">
-        <v>6832652</v>
+        <v>6832663</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125707417</v>
+        <v>125706791</v>
       </c>
       <c r="B6" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495819</v>
+        <v>495730</v>
       </c>
       <c r="R6" t="n">
-        <v>6832571</v>
+        <v>6832652</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125706913</v>
+        <v>125707417</v>
       </c>
       <c r="B7" t="n">
-        <v>92518</v>
+        <v>79590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495727</v>
+        <v>495819</v>
       </c>
       <c r="R7" t="n">
-        <v>6832609</v>
+        <v>6832571</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
         <v>125708227</v>
       </c>
       <c r="B8" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125707173</v>
+        <v>125706524</v>
       </c>
       <c r="B9" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495761</v>
+        <v>495786</v>
       </c>
       <c r="R9" t="n">
-        <v>6832581</v>
+        <v>6832670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125707511</v>
+        <v>125707173</v>
       </c>
       <c r="B10" t="n">
-        <v>80071</v>
+        <v>79004</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495780</v>
+        <v>495761</v>
       </c>
       <c r="R10" t="n">
-        <v>6832481</v>
+        <v>6832581</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,60 +1536,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125706635</v>
+        <v>125708132</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495776</v>
+        <v>495728</v>
       </c>
       <c r="R11" t="n">
-        <v>6832691</v>
+        <v>6832782</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1642,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125706524</v>
+        <v>125707511</v>
       </c>
       <c r="B12" t="n">
-        <v>79000</v>
+        <v>80075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1689,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495786</v>
+        <v>495780</v>
       </c>
       <c r="R12" t="n">
-        <v>6832670</v>
+        <v>6832481</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,69 +1739,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125708132</v>
+        <v>125706635</v>
       </c>
       <c r="B13" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495728</v>
+        <v>495776</v>
       </c>
       <c r="R13" t="n">
-        <v>6832782</v>
+        <v>6832691</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>125707583</v>
       </c>
       <c r="B14" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>125707544</v>
       </c>
       <c r="B15" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125708856</v>
+        <v>125707655</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,34 +2053,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495902</v>
+        <v>495798</v>
       </c>
       <c r="R16" t="n">
-        <v>6833046</v>
+        <v>6832444</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125707048</v>
+        <v>125708856</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,17 +2170,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495746</v>
+        <v>495902</v>
       </c>
       <c r="R17" t="n">
-        <v>6832627</v>
+        <v>6833046</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2224,22 +2224,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125707655</v>
+        <v>125707048</v>
       </c>
       <c r="B18" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495798</v>
+        <v>495746</v>
       </c>
       <c r="R18" t="n">
-        <v>6832444</v>
+        <v>6832627</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2321,22 +2321,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125708470</v>
+        <v>125706678</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495718</v>
+        <v>495780</v>
       </c>
       <c r="R19" t="n">
-        <v>6832947</v>
+        <v>6832667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2418,22 +2418,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125706678</v>
+        <v>125708470</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495780</v>
+        <v>495718</v>
       </c>
       <c r="R20" t="n">
-        <v>6832667</v>
+        <v>6832947</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2515,12 +2515,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
         <v>125708060</v>
       </c>
       <c r="B21" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>125706549</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,48 +2730,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125706788</v>
+        <v>125707033</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495756</v>
+        <v>495733</v>
       </c>
       <c r="R23" t="n">
-        <v>6832675</v>
+        <v>6832598</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2815,69 +2824,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125707033</v>
+        <v>125706777</v>
       </c>
       <c r="B24" t="n">
-        <v>98334</v>
+        <v>79004</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495733</v>
+        <v>495767</v>
       </c>
       <c r="R24" t="n">
-        <v>6832598</v>
+        <v>6832677</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2921,22 +2921,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125706777</v>
+        <v>125707543</v>
       </c>
       <c r="B25" t="n">
-        <v>79000</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495767</v>
+        <v>495772</v>
       </c>
       <c r="R25" t="n">
-        <v>6832677</v>
+        <v>6832482</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125707543</v>
+        <v>125706788</v>
       </c>
       <c r="B26" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3041,21 +3041,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495772</v>
+        <v>495756</v>
       </c>
       <c r="R26" t="n">
-        <v>6832482</v>
+        <v>6832675</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3115,44 +3115,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125706444</v>
+        <v>125706487</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495750</v>
+        <v>495759</v>
       </c>
       <c r="R27" t="n">
-        <v>6832709</v>
+        <v>6832688</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3224,32 +3224,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125706487</v>
+        <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495759</v>
+        <v>495750</v>
       </c>
       <c r="R28" t="n">
-        <v>6832688</v>
+        <v>6832709</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125708014</v>
+        <v>125707016</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495817</v>
+        <v>495749</v>
       </c>
       <c r="R29" t="n">
-        <v>6832682</v>
+        <v>6832629</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125706538</v>
+        <v>125707083</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495769</v>
+        <v>495751</v>
       </c>
       <c r="R30" t="n">
-        <v>6832671</v>
+        <v>6832612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125707016</v>
+        <v>125706637</v>
       </c>
       <c r="B31" t="n">
-        <v>79000</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,21 +3526,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3550,13 +3550,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495749</v>
+        <v>495737</v>
       </c>
       <c r="R31" t="n">
-        <v>6832629</v>
+        <v>6832680</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3600,22 +3600,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125707083</v>
+        <v>125708848</v>
       </c>
       <c r="B32" t="n">
-        <v>79000</v>
+        <v>80075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495751</v>
+        <v>495680</v>
       </c>
       <c r="R32" t="n">
-        <v>6832612</v>
+        <v>6832870</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125706637</v>
+        <v>125706538</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495737</v>
+        <v>495769</v>
       </c>
       <c r="R33" t="n">
-        <v>6832680</v>
+        <v>6832671</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3794,22 +3794,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125708848</v>
+        <v>125708014</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495680</v>
+        <v>495817</v>
       </c>
       <c r="R34" t="n">
-        <v>6832870</v>
+        <v>6832682</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>125708314</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>125706445</v>
       </c>
       <c r="B36" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4115,57 +4115,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125707003</v>
+        <v>125706917</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>79004</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495724</v>
+        <v>495776</v>
       </c>
       <c r="R37" t="n">
-        <v>6832599</v>
+        <v>6832649</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4209,22 +4200,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B38" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R38" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,10 +4309,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706947</v>
+        <v>125707384</v>
       </c>
       <c r="B39" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4329,21 +4320,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4353,13 +4344,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495763</v>
+        <v>495765</v>
       </c>
       <c r="R39" t="n">
-        <v>6832629</v>
+        <v>6832558</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4403,57 +4394,66 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707384</v>
+        <v>125707003</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495765</v>
+        <v>495724</v>
       </c>
       <c r="R40" t="n">
-        <v>6832558</v>
+        <v>6832599</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4515,7 +4515,7 @@
         <v>125706892</v>
       </c>
       <c r="B41" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,32 +4609,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125706691</v>
+        <v>125707372</v>
       </c>
       <c r="B42" t="n">
-        <v>78992</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495777</v>
+        <v>495764</v>
       </c>
       <c r="R42" t="n">
-        <v>6832671</v>
+        <v>6832553</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4694,44 +4694,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125707372</v>
+        <v>125706691</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78996</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495764</v>
+        <v>495777</v>
       </c>
       <c r="R43" t="n">
-        <v>6832553</v>
+        <v>6832671</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4791,12 +4791,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
         <v>125706714</v>
       </c>
       <c r="B44" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,45 +4909,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125706720</v>
+        <v>125708266</v>
       </c>
       <c r="B45" t="n">
-        <v>79000</v>
+        <v>98338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495782</v>
+        <v>495706</v>
       </c>
       <c r="R45" t="n">
-        <v>6832661</v>
+        <v>6832880</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5006,63 +5015,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125707718</v>
+        <v>125706720</v>
       </c>
       <c r="B46" t="n">
-        <v>56843</v>
+        <v>79004</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495818</v>
+        <v>495782</v>
       </c>
       <c r="R46" t="n">
-        <v>6832436</v>
+        <v>6832661</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5106,54 +5100,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708266</v>
+        <v>125707718</v>
       </c>
       <c r="B47" t="n">
-        <v>98334</v>
+        <v>56843</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495706</v>
+        <v>495818</v>
       </c>
       <c r="R47" t="n">
-        <v>6832880</v>
+        <v>6832436</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5212,12 +5212,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5227,7 +5227,7 @@
         <v>125706842</v>
       </c>
       <c r="B48" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125707108</v>
+        <v>125706827</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5332,21 +5332,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495743</v>
+        <v>495745</v>
       </c>
       <c r="R49" t="n">
-        <v>6832597</v>
+        <v>6832669</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5418,10 +5418,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125706827</v>
+        <v>125707108</v>
       </c>
       <c r="B50" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,21 +5429,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495745</v>
+        <v>495743</v>
       </c>
       <c r="R50" t="n">
-        <v>6832669</v>
+        <v>6832597</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5621,48 +5621,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125706764</v>
+        <v>125707479</v>
       </c>
       <c r="B52" t="n">
-        <v>79000</v>
+        <v>98338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495761</v>
+        <v>495776</v>
       </c>
       <c r="R52" t="n">
-        <v>6832671</v>
+        <v>6832485</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5706,60 +5715,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125708210</v>
+        <v>125706779</v>
       </c>
       <c r="B53" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495705</v>
+        <v>495724</v>
       </c>
       <c r="R53" t="n">
-        <v>6832884</v>
+        <v>6832662</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5803,22 +5821,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706943</v>
+        <v>125706764</v>
       </c>
       <c r="B54" t="n">
-        <v>80071</v>
+        <v>79004</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,21 +5844,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5850,13 +5868,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495715</v>
+        <v>495761</v>
       </c>
       <c r="R54" t="n">
-        <v>6832599</v>
+        <v>6832671</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5900,22 +5918,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708307</v>
+        <v>125708210</v>
       </c>
       <c r="B55" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5947,13 +5965,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495712</v>
+        <v>495705</v>
       </c>
       <c r="R55" t="n">
-        <v>6832874</v>
+        <v>6832884</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5997,44 +6015,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125707134</v>
+        <v>125706943</v>
       </c>
       <c r="B56" t="n">
-        <v>56958</v>
+        <v>80075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6044,10 +6062,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495770</v>
+        <v>495715</v>
       </c>
       <c r="R56" t="n">
-        <v>6832555</v>
+        <v>6832599</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6106,54 +6124,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125707479</v>
+        <v>125708307</v>
       </c>
       <c r="B57" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495776</v>
+        <v>495712</v>
       </c>
       <c r="R57" t="n">
-        <v>6832485</v>
+        <v>6832874</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6212,54 +6221,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125706779</v>
+        <v>125707134</v>
       </c>
       <c r="B58" t="n">
-        <v>98334</v>
+        <v>56958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495724</v>
+        <v>495770</v>
       </c>
       <c r="R58" t="n">
-        <v>6832662</v>
+        <v>6832555</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125707093</v>
+        <v>125707413</v>
       </c>
       <c r="B59" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495727</v>
+        <v>495782</v>
       </c>
       <c r="R59" t="n">
-        <v>6832581</v>
+        <v>6832513</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707413</v>
+        <v>125707093</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6426,21 +6426,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495782</v>
+        <v>495727</v>
       </c>
       <c r="R60" t="n">
-        <v>6832513</v>
+        <v>6832581</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6515,7 +6515,7 @@
         <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,48 +6618,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125706395</v>
+        <v>125707073</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495818</v>
+        <v>495738</v>
       </c>
       <c r="R62" t="n">
-        <v>6832725</v>
+        <v>6832601</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6718,7 +6727,7 @@
         <v>125707370</v>
       </c>
       <c r="B63" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,57 +6821,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B64" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R64" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708074</v>
+        <v>125708583</v>
       </c>
       <c r="B65" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,34 +6929,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495733</v>
+        <v>495841</v>
       </c>
       <c r="R65" t="n">
-        <v>6832780</v>
+        <v>6833181</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125708596</v>
+        <v>125708074</v>
       </c>
       <c r="B66" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7050,13 +7050,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495930</v>
+        <v>495733</v>
       </c>
       <c r="R66" t="n">
-        <v>6833128</v>
+        <v>6832780</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7100,22 +7100,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125706873</v>
+        <v>125708596</v>
       </c>
       <c r="B67" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495718</v>
+        <v>495930</v>
       </c>
       <c r="R67" t="n">
-        <v>6832621</v>
+        <v>6833128</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7197,22 +7197,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125708583</v>
+        <v>125706873</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,34 +7220,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495841</v>
+        <v>495718</v>
       </c>
       <c r="R68" t="n">
-        <v>6833181</v>
+        <v>6832621</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -2333,48 +2333,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125706678</v>
+        <v>125708060</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>98338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495780</v>
+        <v>495753</v>
       </c>
       <c r="R19" t="n">
-        <v>6832667</v>
+        <v>6832752</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2418,22 +2427,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125708470</v>
+        <v>125706678</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2450,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495718</v>
+        <v>495780</v>
       </c>
       <c r="R20" t="n">
-        <v>6832947</v>
+        <v>6832667</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2515,69 +2524,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125708060</v>
+        <v>125708470</v>
       </c>
       <c r="B21" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495753</v>
+        <v>495718</v>
       </c>
       <c r="R21" t="n">
-        <v>6832752</v>
+        <v>6832947</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2730,57 +2730,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125707033</v>
+        <v>125706777</v>
       </c>
       <c r="B23" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495733</v>
+        <v>495767</v>
       </c>
       <c r="R23" t="n">
-        <v>6832598</v>
+        <v>6832677</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2824,22 +2815,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125706777</v>
+        <v>125707543</v>
       </c>
       <c r="B24" t="n">
-        <v>79004</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,21 +2838,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2871,13 +2862,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495767</v>
+        <v>495772</v>
       </c>
       <c r="R24" t="n">
-        <v>6832677</v>
+        <v>6832482</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2921,22 +2912,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125707543</v>
+        <v>125706788</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2935,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,13 +2959,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495772</v>
+        <v>495756</v>
       </c>
       <c r="R25" t="n">
-        <v>6832482</v>
+        <v>6832675</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3018,60 +3009,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125706788</v>
+        <v>125707033</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495756</v>
+        <v>495733</v>
       </c>
       <c r="R26" t="n">
-        <v>6832675</v>
+        <v>6832598</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3115,12 +3115,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4115,48 +4115,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125706917</v>
+        <v>125707003</v>
       </c>
       <c r="B37" t="n">
-        <v>79004</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495776</v>
+        <v>495724</v>
       </c>
       <c r="R37" t="n">
-        <v>6832649</v>
+        <v>6832599</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4200,19 +4209,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706947</v>
+        <v>125706917</v>
       </c>
       <c r="B38" t="n">
         <v>79004</v>
@@ -4247,10 +4256,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495763</v>
+        <v>495776</v>
       </c>
       <c r="R38" t="n">
-        <v>6832629</v>
+        <v>6832649</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,10 +4318,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125707384</v>
+        <v>125706947</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4320,21 +4329,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,13 +4353,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495765</v>
+        <v>495763</v>
       </c>
       <c r="R39" t="n">
-        <v>6832558</v>
+        <v>6832629</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4394,66 +4403,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707003</v>
+        <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495724</v>
+        <v>495765</v>
       </c>
       <c r="R40" t="n">
-        <v>6832599</v>
+        <v>6832558</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4909,42 +4909,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125708266</v>
+        <v>125707718</v>
       </c>
       <c r="B45" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4953,13 +4959,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495706</v>
+        <v>495818</v>
       </c>
       <c r="R45" t="n">
-        <v>6832880</v>
+        <v>6832436</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5003,57 +5009,66 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125706720</v>
+        <v>125708266</v>
       </c>
       <c r="B46" t="n">
-        <v>79004</v>
+        <v>98338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495782</v>
+        <v>495706</v>
       </c>
       <c r="R46" t="n">
-        <v>6832661</v>
+        <v>6832880</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5112,63 +5127,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125707718</v>
+        <v>125706720</v>
       </c>
       <c r="B47" t="n">
-        <v>56843</v>
+        <v>79004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495818</v>
+        <v>495782</v>
       </c>
       <c r="R47" t="n">
-        <v>6832436</v>
+        <v>6832661</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5212,12 +5212,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6618,57 +6618,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B62" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R62" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6724,48 +6715,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125707370</v>
+        <v>125707073</v>
       </c>
       <c r="B63" t="n">
-        <v>79004</v>
+        <v>98338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495793</v>
+        <v>495738</v>
       </c>
       <c r="R63" t="n">
-        <v>6832568</v>
+        <v>6832601</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6809,22 +6809,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R64" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,12 +6906,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125706913</v>
+        <v>125706872</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>79004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495727</v>
+        <v>495765</v>
       </c>
       <c r="R4" t="n">
-        <v>6832609</v>
+        <v>6832663</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706872</v>
+        <v>125706791</v>
       </c>
       <c r="B5" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495765</v>
+        <v>495730</v>
       </c>
       <c r="R5" t="n">
-        <v>6832663</v>
+        <v>6832652</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125706791</v>
+        <v>125707417</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495730</v>
+        <v>495819</v>
       </c>
       <c r="R6" t="n">
-        <v>6832652</v>
+        <v>6832571</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125707417</v>
+        <v>125708227</v>
       </c>
       <c r="B7" t="n">
-        <v>79590</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495819</v>
+        <v>495692</v>
       </c>
       <c r="R7" t="n">
-        <v>6832571</v>
+        <v>6832878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125708227</v>
+        <v>125706913</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>92522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495692</v>
+        <v>495727</v>
       </c>
       <c r="R8" t="n">
-        <v>6832878</v>
+        <v>6832609</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1548,54 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125708132</v>
+        <v>125707511</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495728</v>
+        <v>495780</v>
       </c>
       <c r="R11" t="n">
-        <v>6832782</v>
+        <v>6832481</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1654,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125707511</v>
+        <v>125706635</v>
       </c>
       <c r="B12" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495780</v>
+        <v>495776</v>
       </c>
       <c r="R12" t="n">
-        <v>6832481</v>
+        <v>6832691</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1739,60 +1730,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125706635</v>
+        <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495776</v>
+        <v>495728</v>
       </c>
       <c r="R13" t="n">
-        <v>6832691</v>
+        <v>6832782</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125707655</v>
+        <v>125707048</v>
       </c>
       <c r="B16" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495798</v>
+        <v>495746</v>
       </c>
       <c r="R16" t="n">
-        <v>6832444</v>
+        <v>6832627</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125708856</v>
+        <v>125707655</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495902</v>
+        <v>495798</v>
       </c>
       <c r="R17" t="n">
-        <v>6833046</v>
+        <v>6832444</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125707048</v>
+        <v>125708856</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2267,17 +2267,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495746</v>
+        <v>495902</v>
       </c>
       <c r="R18" t="n">
-        <v>6832627</v>
+        <v>6833046</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2321,69 +2321,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125708060</v>
+        <v>125708470</v>
       </c>
       <c r="B19" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495753</v>
+        <v>495718</v>
       </c>
       <c r="R19" t="n">
-        <v>6832752</v>
+        <v>6832947</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2439,48 +2430,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125706678</v>
+        <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495780</v>
+        <v>495753</v>
       </c>
       <c r="R20" t="n">
-        <v>6832667</v>
+        <v>6832752</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2524,22 +2524,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125708470</v>
+        <v>125706678</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495718</v>
+        <v>495780</v>
       </c>
       <c r="R21" t="n">
-        <v>6832947</v>
+        <v>6832667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,12 +2621,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125706777</v>
+        <v>125707543</v>
       </c>
       <c r="B23" t="n">
-        <v>79004</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495767</v>
+        <v>495772</v>
       </c>
       <c r="R23" t="n">
-        <v>6832677</v>
+        <v>6832482</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2815,57 +2815,66 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125707543</v>
+        <v>125707033</v>
       </c>
       <c r="B24" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495772</v>
+        <v>495733</v>
       </c>
       <c r="R24" t="n">
-        <v>6832482</v>
+        <v>6832598</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2924,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125706788</v>
+        <v>125706777</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2935,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2959,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495756</v>
+        <v>495767</v>
       </c>
       <c r="R25" t="n">
-        <v>6832675</v>
+        <v>6832677</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,57 +3030,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125707033</v>
+        <v>125706788</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495733</v>
+        <v>495756</v>
       </c>
       <c r="R26" t="n">
-        <v>6832598</v>
+        <v>6832675</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3115,12 +3115,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
         <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125707016</v>
+        <v>125708014</v>
       </c>
       <c r="B29" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495749</v>
+        <v>495817</v>
       </c>
       <c r="R29" t="n">
-        <v>6832629</v>
+        <v>6832682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125707083</v>
+        <v>125706538</v>
       </c>
       <c r="B30" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495751</v>
+        <v>495769</v>
       </c>
       <c r="R30" t="n">
-        <v>6832612</v>
+        <v>6832671</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,48 +3515,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125706637</v>
+        <v>125706445</v>
       </c>
       <c r="B31" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495737</v>
+        <v>495778</v>
       </c>
       <c r="R31" t="n">
-        <v>6832680</v>
+        <v>6832690</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3600,57 +3609,66 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125708848</v>
+        <v>125708314</v>
       </c>
       <c r="B32" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495680</v>
+        <v>495700</v>
       </c>
       <c r="R32" t="n">
-        <v>6832870</v>
+        <v>6832875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125706538</v>
+        <v>125707016</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3720,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3744,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495769</v>
+        <v>495749</v>
       </c>
       <c r="R33" t="n">
-        <v>6832671</v>
+        <v>6832629</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125708014</v>
+        <v>125707083</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3817,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3841,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495817</v>
+        <v>495751</v>
       </c>
       <c r="R34" t="n">
-        <v>6832682</v>
+        <v>6832612</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3903,57 +3921,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125708314</v>
+        <v>125706637</v>
       </c>
       <c r="B35" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495700</v>
+        <v>495737</v>
       </c>
       <c r="R35" t="n">
-        <v>6832875</v>
+        <v>6832680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3997,66 +4006,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125706445</v>
+        <v>125708848</v>
       </c>
       <c r="B36" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495778</v>
+        <v>495680</v>
       </c>
       <c r="R36" t="n">
-        <v>6832690</v>
+        <v>6832870</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4118,7 +4118,7 @@
         <v>125707003</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>125706714</v>
       </c>
       <c r="B44" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,63 +4909,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125707718</v>
+        <v>125706720</v>
       </c>
       <c r="B45" t="n">
-        <v>56843</v>
+        <v>79004</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495818</v>
+        <v>495782</v>
       </c>
       <c r="R45" t="n">
-        <v>6832436</v>
+        <v>6832661</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5009,54 +4994,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125708266</v>
+        <v>125707718</v>
       </c>
       <c r="B46" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5065,13 +5056,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495706</v>
+        <v>495818</v>
       </c>
       <c r="R46" t="n">
-        <v>6832880</v>
+        <v>6832436</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5115,57 +5106,66 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125706720</v>
+        <v>125708266</v>
       </c>
       <c r="B47" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495782</v>
+        <v>495706</v>
       </c>
       <c r="R47" t="n">
-        <v>6832661</v>
+        <v>6832880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5224,45 +5224,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125706842</v>
+        <v>125707720</v>
       </c>
       <c r="B48" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495760</v>
+        <v>495839</v>
       </c>
       <c r="R48" t="n">
-        <v>6832666</v>
+        <v>6832437</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,10 +5330,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125706827</v>
+        <v>125706842</v>
       </c>
       <c r="B49" t="n">
-        <v>78730</v>
+        <v>79004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5332,21 +5341,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5356,10 +5365,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495745</v>
+        <v>495760</v>
       </c>
       <c r="R49" t="n">
-        <v>6832669</v>
+        <v>6832666</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5418,10 +5427,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125707108</v>
+        <v>125706827</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,21 +5438,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5453,10 +5462,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495743</v>
+        <v>495745</v>
       </c>
       <c r="R50" t="n">
-        <v>6832597</v>
+        <v>6832669</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5515,54 +5524,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125707720</v>
+        <v>125707108</v>
       </c>
       <c r="B51" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495839</v>
+        <v>495743</v>
       </c>
       <c r="R51" t="n">
-        <v>6832437</v>
+        <v>6832597</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,57 +5621,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125707479</v>
+        <v>125706764</v>
       </c>
       <c r="B52" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495776</v>
+        <v>495761</v>
       </c>
       <c r="R52" t="n">
-        <v>6832485</v>
+        <v>6832671</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5715,69 +5706,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125706779</v>
+        <v>125708210</v>
       </c>
       <c r="B53" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495724</v>
+        <v>495705</v>
       </c>
       <c r="R53" t="n">
-        <v>6832662</v>
+        <v>6832884</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5821,22 +5803,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706764</v>
+        <v>125706943</v>
       </c>
       <c r="B54" t="n">
-        <v>79004</v>
+        <v>80075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5844,21 +5826,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5868,13 +5850,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495761</v>
+        <v>495715</v>
       </c>
       <c r="R54" t="n">
-        <v>6832671</v>
+        <v>6832599</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5918,19 +5900,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708210</v>
+        <v>125708307</v>
       </c>
       <c r="B55" t="n">
         <v>80075</v>
@@ -5965,13 +5947,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495705</v>
+        <v>495712</v>
       </c>
       <c r="R55" t="n">
-        <v>6832884</v>
+        <v>6832874</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6015,44 +5997,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706943</v>
+        <v>125707134</v>
       </c>
       <c r="B56" t="n">
-        <v>80075</v>
+        <v>56958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6062,10 +6044,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495715</v>
+        <v>495770</v>
       </c>
       <c r="R56" t="n">
-        <v>6832599</v>
+        <v>6832555</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6124,45 +6106,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125708307</v>
+        <v>125706779</v>
       </c>
       <c r="B57" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495712</v>
+        <v>495724</v>
       </c>
       <c r="R57" t="n">
-        <v>6832874</v>
+        <v>6832662</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6221,45 +6212,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125707134</v>
+        <v>125707479</v>
       </c>
       <c r="B58" t="n">
-        <v>56958</v>
+        <v>98339</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495770</v>
+        <v>495776</v>
       </c>
       <c r="R58" t="n">
-        <v>6832555</v>
+        <v>6832485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6515,7 +6515,7 @@
         <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R62" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,12 +6703,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6718,7 +6718,7 @@
         <v>125707073</v>
       </c>
       <c r="B63" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707370</v>
+        <v>125706395</v>
       </c>
       <c r="B64" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495793</v>
+        <v>495818</v>
       </c>
       <c r="R64" t="n">
-        <v>6832568</v>
+        <v>6832725</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,12 +6906,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -3127,32 +3127,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125706487</v>
+        <v>125706444</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495759</v>
+        <v>495750</v>
       </c>
       <c r="R27" t="n">
-        <v>6832688</v>
+        <v>6832709</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3224,32 +3224,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125706444</v>
+        <v>125706487</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495750</v>
+        <v>495759</v>
       </c>
       <c r="R28" t="n">
-        <v>6832709</v>
+        <v>6832688</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706917</v>
+        <v>125707384</v>
       </c>
       <c r="B38" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4232,21 +4232,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495776</v>
+        <v>495765</v>
       </c>
       <c r="R38" t="n">
-        <v>6832649</v>
+        <v>6832558</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4306,19 +4306,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706947</v>
+        <v>125706917</v>
       </c>
       <c r="B39" t="n">
         <v>79004</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495763</v>
+        <v>495776</v>
       </c>
       <c r="R39" t="n">
-        <v>6832629</v>
+        <v>6832649</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,10 +4415,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707384</v>
+        <v>125706947</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4426,21 +4426,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4450,13 +4450,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495765</v>
+        <v>495763</v>
       </c>
       <c r="R40" t="n">
-        <v>6832558</v>
+        <v>6832629</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4500,12 +4500,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5224,54 +5224,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125707720</v>
+        <v>125706827</v>
       </c>
       <c r="B48" t="n">
-        <v>98339</v>
+        <v>78730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495839</v>
+        <v>495745</v>
       </c>
       <c r="R48" t="n">
-        <v>6832437</v>
+        <v>6832669</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5330,45 +5321,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125706842</v>
+        <v>125707720</v>
       </c>
       <c r="B49" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495760</v>
+        <v>495839</v>
       </c>
       <c r="R49" t="n">
-        <v>6832666</v>
+        <v>6832437</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125706827</v>
+        <v>125706842</v>
       </c>
       <c r="B50" t="n">
-        <v>78730</v>
+        <v>79004</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5438,21 +5438,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495745</v>
+        <v>495760</v>
       </c>
       <c r="R50" t="n">
-        <v>6832669</v>
+        <v>6832666</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5621,48 +5621,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125706764</v>
+        <v>125706779</v>
       </c>
       <c r="B52" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495761</v>
+        <v>495724</v>
       </c>
       <c r="R52" t="n">
-        <v>6832671</v>
+        <v>6832662</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5706,60 +5715,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125708210</v>
+        <v>125707479</v>
       </c>
       <c r="B53" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495705</v>
+        <v>495776</v>
       </c>
       <c r="R53" t="n">
-        <v>6832884</v>
+        <v>6832485</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5803,22 +5821,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706943</v>
+        <v>125706764</v>
       </c>
       <c r="B54" t="n">
-        <v>80075</v>
+        <v>79004</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,21 +5844,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5850,13 +5868,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495715</v>
+        <v>495761</v>
       </c>
       <c r="R54" t="n">
-        <v>6832599</v>
+        <v>6832671</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5900,19 +5918,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708307</v>
+        <v>125708210</v>
       </c>
       <c r="B55" t="n">
         <v>80075</v>
@@ -5947,13 +5965,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495712</v>
+        <v>495705</v>
       </c>
       <c r="R55" t="n">
-        <v>6832874</v>
+        <v>6832884</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5997,44 +6015,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125707134</v>
+        <v>125706943</v>
       </c>
       <c r="B56" t="n">
-        <v>56958</v>
+        <v>80075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6044,10 +6062,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495770</v>
+        <v>495715</v>
       </c>
       <c r="R56" t="n">
-        <v>6832555</v>
+        <v>6832599</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6106,54 +6124,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125706779</v>
+        <v>125708307</v>
       </c>
       <c r="B57" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495724</v>
+        <v>495712</v>
       </c>
       <c r="R57" t="n">
-        <v>6832662</v>
+        <v>6832874</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6212,54 +6221,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125707479</v>
+        <v>125707134</v>
       </c>
       <c r="B58" t="n">
-        <v>98339</v>
+        <v>56958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495776</v>
+        <v>495770</v>
       </c>
       <c r="R58" t="n">
-        <v>6832485</v>
+        <v>6832555</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6715,57 +6715,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B63" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R63" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6821,48 +6812,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125706395</v>
+        <v>125707073</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495818</v>
+        <v>495738</v>
       </c>
       <c r="R64" t="n">
-        <v>6832725</v>
+        <v>6832601</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706791</v>
+        <v>125708227</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495730</v>
+        <v>495692</v>
       </c>
       <c r="R5" t="n">
-        <v>6832652</v>
+        <v>6832878</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125707417</v>
+        <v>125706913</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495819</v>
+        <v>495727</v>
       </c>
       <c r="R6" t="n">
-        <v>6832571</v>
+        <v>6832609</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125708227</v>
+        <v>125706791</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495692</v>
+        <v>495730</v>
       </c>
       <c r="R7" t="n">
-        <v>6832878</v>
+        <v>6832652</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125706913</v>
+        <v>125707417</v>
       </c>
       <c r="B8" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495727</v>
+        <v>495819</v>
       </c>
       <c r="R8" t="n">
-        <v>6832609</v>
+        <v>6832571</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2730,45 +2730,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125707543</v>
+        <v>125707033</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495772</v>
+        <v>495733</v>
       </c>
       <c r="R23" t="n">
-        <v>6832482</v>
+        <v>6832598</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2827,57 +2836,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125707033</v>
+        <v>125706777</v>
       </c>
       <c r="B24" t="n">
-        <v>98339</v>
+        <v>79004</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495733</v>
+        <v>495767</v>
       </c>
       <c r="R24" t="n">
-        <v>6832598</v>
+        <v>6832677</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2921,22 +2921,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125706777</v>
+        <v>125707543</v>
       </c>
       <c r="B25" t="n">
-        <v>79004</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495767</v>
+        <v>495772</v>
       </c>
       <c r="R25" t="n">
-        <v>6832677</v>
+        <v>6832482</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3018,12 +3018,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3127,32 +3127,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125706444</v>
+        <v>125706487</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495750</v>
+        <v>495759</v>
       </c>
       <c r="R27" t="n">
-        <v>6832709</v>
+        <v>6832688</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3224,32 +3224,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125706487</v>
+        <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495759</v>
+        <v>495750</v>
       </c>
       <c r="R28" t="n">
-        <v>6832688</v>
+        <v>6832709</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125708014</v>
+        <v>125707016</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495817</v>
+        <v>495749</v>
       </c>
       <c r="R29" t="n">
-        <v>6832682</v>
+        <v>6832629</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125706538</v>
+        <v>125707083</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495769</v>
+        <v>495751</v>
       </c>
       <c r="R30" t="n">
-        <v>6832671</v>
+        <v>6832612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,57 +3515,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125706445</v>
+        <v>125706637</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495778</v>
+        <v>495737</v>
       </c>
       <c r="R31" t="n">
-        <v>6832690</v>
+        <v>6832680</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3609,66 +3600,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125708314</v>
+        <v>125708848</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495700</v>
+        <v>495680</v>
       </c>
       <c r="R32" t="n">
-        <v>6832875</v>
+        <v>6832870</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,10 +3709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125707016</v>
+        <v>125708014</v>
       </c>
       <c r="B33" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3720,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495749</v>
+        <v>495817</v>
       </c>
       <c r="R33" t="n">
-        <v>6832629</v>
+        <v>6832682</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3806,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125707083</v>
+        <v>125706538</v>
       </c>
       <c r="B34" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3817,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495751</v>
+        <v>495769</v>
       </c>
       <c r="R34" t="n">
-        <v>6832612</v>
+        <v>6832671</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,48 +3903,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125706637</v>
+        <v>125706445</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495737</v>
+        <v>495778</v>
       </c>
       <c r="R35" t="n">
-        <v>6832680</v>
+        <v>6832690</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4006,57 +3997,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125708848</v>
+        <v>125708314</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495680</v>
+        <v>495700</v>
       </c>
       <c r="R36" t="n">
-        <v>6832870</v>
+        <v>6832875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125707384</v>
+        <v>125706917</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4232,21 +4232,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495765</v>
+        <v>495776</v>
       </c>
       <c r="R38" t="n">
-        <v>6832558</v>
+        <v>6832649</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4306,19 +4306,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B39" t="n">
         <v>79004</v>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R39" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,10 +4415,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125706947</v>
+        <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4426,21 +4426,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4450,13 +4450,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495763</v>
+        <v>495765</v>
       </c>
       <c r="R40" t="n">
-        <v>6832629</v>
+        <v>6832558</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4500,12 +4500,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125706827</v>
+        <v>125706842</v>
       </c>
       <c r="B48" t="n">
-        <v>78730</v>
+        <v>79004</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495745</v>
+        <v>495760</v>
       </c>
       <c r="R48" t="n">
-        <v>6832669</v>
+        <v>6832666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,54 +5321,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125707720</v>
+        <v>125706827</v>
       </c>
       <c r="B49" t="n">
-        <v>98339</v>
+        <v>78730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495839</v>
+        <v>495745</v>
       </c>
       <c r="R49" t="n">
-        <v>6832437</v>
+        <v>6832669</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,10 +5418,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125706842</v>
+        <v>125707108</v>
       </c>
       <c r="B50" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5438,21 +5429,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5462,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495760</v>
+        <v>495743</v>
       </c>
       <c r="R50" t="n">
-        <v>6832666</v>
+        <v>6832597</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5524,45 +5515,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125707108</v>
+        <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495743</v>
+        <v>495839</v>
       </c>
       <c r="R51" t="n">
-        <v>6832597</v>
+        <v>6832437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,57 +5621,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125706779</v>
+        <v>125708210</v>
       </c>
       <c r="B52" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495724</v>
+        <v>495705</v>
       </c>
       <c r="R52" t="n">
-        <v>6832662</v>
+        <v>6832884</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5715,66 +5706,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125707479</v>
+        <v>125706943</v>
       </c>
       <c r="B53" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495776</v>
+        <v>495715</v>
       </c>
       <c r="R53" t="n">
-        <v>6832485</v>
+        <v>6832599</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5833,10 +5815,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706764</v>
+        <v>125708307</v>
       </c>
       <c r="B54" t="n">
-        <v>79004</v>
+        <v>80075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5844,21 +5826,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5868,13 +5850,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495761</v>
+        <v>495712</v>
       </c>
       <c r="R54" t="n">
-        <v>6832671</v>
+        <v>6832874</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5918,44 +5900,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708210</v>
+        <v>125707134</v>
       </c>
       <c r="B55" t="n">
-        <v>80075</v>
+        <v>56958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5965,13 +5947,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495705</v>
+        <v>495770</v>
       </c>
       <c r="R55" t="n">
-        <v>6832884</v>
+        <v>6832555</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6015,22 +5997,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706943</v>
+        <v>125706764</v>
       </c>
       <c r="B56" t="n">
-        <v>80075</v>
+        <v>79004</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6038,21 +6020,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6062,13 +6044,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495715</v>
+        <v>495761</v>
       </c>
       <c r="R56" t="n">
-        <v>6832599</v>
+        <v>6832671</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6112,57 +6094,66 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125708307</v>
+        <v>125706779</v>
       </c>
       <c r="B57" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495712</v>
+        <v>495724</v>
       </c>
       <c r="R57" t="n">
-        <v>6832874</v>
+        <v>6832662</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6221,45 +6212,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125707134</v>
+        <v>125707479</v>
       </c>
       <c r="B58" t="n">
-        <v>56958</v>
+        <v>98339</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495770</v>
+        <v>495776</v>
       </c>
       <c r="R58" t="n">
-        <v>6832555</v>
+        <v>6832485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125708078</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125707087</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125706872</v>
+        <v>125707417</v>
       </c>
       <c r="B4" t="n">
-        <v>79004</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495765</v>
+        <v>495819</v>
       </c>
       <c r="R4" t="n">
-        <v>6832663</v>
+        <v>6832571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125708227</v>
+        <v>125706791</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495692</v>
+        <v>495730</v>
       </c>
       <c r="R5" t="n">
-        <v>6832878</v>
+        <v>6832652</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125706913</v>
+        <v>125708227</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>80077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495727</v>
+        <v>495692</v>
       </c>
       <c r="R6" t="n">
-        <v>6832609</v>
+        <v>6832878</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125706791</v>
+        <v>125706913</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>92524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495730</v>
+        <v>495727</v>
       </c>
       <c r="R7" t="n">
-        <v>6832652</v>
+        <v>6832609</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125707417</v>
+        <v>125706872</v>
       </c>
       <c r="B8" t="n">
-        <v>79590</v>
+        <v>79005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495819</v>
+        <v>495765</v>
       </c>
       <c r="R8" t="n">
-        <v>6832571</v>
+        <v>6832663</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125706524</v>
+        <v>125707511</v>
       </c>
       <c r="B9" t="n">
-        <v>79004</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495786</v>
+        <v>495780</v>
       </c>
       <c r="R9" t="n">
-        <v>6832670</v>
+        <v>6832481</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125707173</v>
+        <v>125706635</v>
       </c>
       <c r="B10" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495761</v>
+        <v>495776</v>
       </c>
       <c r="R10" t="n">
-        <v>6832581</v>
+        <v>6832691</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125707511</v>
+        <v>125706524</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>79005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495780</v>
+        <v>495786</v>
       </c>
       <c r="R11" t="n">
-        <v>6832481</v>
+        <v>6832670</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125706635</v>
+        <v>125707173</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495776</v>
+        <v>495761</v>
       </c>
       <c r="R12" t="n">
-        <v>6832691</v>
+        <v>6832581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>125707583</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125707544</v>
+        <v>125707048</v>
       </c>
       <c r="B15" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495877</v>
+        <v>495746</v>
       </c>
       <c r="R15" t="n">
-        <v>6832537</v>
+        <v>6832627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125707048</v>
+        <v>125707544</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495746</v>
+        <v>495877</v>
       </c>
       <c r="R16" t="n">
-        <v>6832627</v>
+        <v>6832537</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
         <v>125707655</v>
       </c>
       <c r="B17" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>125708856</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>125708470</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>125706678</v>
       </c>
       <c r="B21" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>125706549</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,57 +2730,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125707033</v>
+        <v>125706777</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495733</v>
+        <v>495767</v>
       </c>
       <c r="R23" t="n">
-        <v>6832598</v>
+        <v>6832677</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2824,22 +2815,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125706777</v>
+        <v>125707543</v>
       </c>
       <c r="B24" t="n">
-        <v>79004</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,21 +2838,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2871,13 +2862,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495767</v>
+        <v>495772</v>
       </c>
       <c r="R24" t="n">
-        <v>6832677</v>
+        <v>6832482</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2921,22 +2912,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125707543</v>
+        <v>125706788</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2935,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,13 +2959,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495772</v>
+        <v>495756</v>
       </c>
       <c r="R25" t="n">
-        <v>6832482</v>
+        <v>6832675</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3018,60 +3009,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125706788</v>
+        <v>125707033</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495756</v>
+        <v>495733</v>
       </c>
       <c r="R26" t="n">
-        <v>6832675</v>
+        <v>6832598</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3115,12 +3115,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3130,7 +3130,7 @@
         <v>125706487</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125707016</v>
+        <v>125706637</v>
       </c>
       <c r="B29" t="n">
-        <v>79004</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495749</v>
+        <v>495737</v>
       </c>
       <c r="R29" t="n">
-        <v>6832629</v>
+        <v>6832680</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3406,22 +3406,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125707083</v>
+        <v>125708848</v>
       </c>
       <c r="B30" t="n">
-        <v>79004</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495751</v>
+        <v>495680</v>
       </c>
       <c r="R30" t="n">
-        <v>6832612</v>
+        <v>6832870</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125706637</v>
+        <v>125707016</v>
       </c>
       <c r="B31" t="n">
-        <v>80075</v>
+        <v>79005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,21 +3526,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3550,13 +3550,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495737</v>
+        <v>495749</v>
       </c>
       <c r="R31" t="n">
-        <v>6832680</v>
+        <v>6832629</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3600,22 +3600,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125708848</v>
+        <v>125707083</v>
       </c>
       <c r="B32" t="n">
-        <v>80075</v>
+        <v>79005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495680</v>
+        <v>495751</v>
       </c>
       <c r="R32" t="n">
-        <v>6832870</v>
+        <v>6832612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125708014</v>
+        <v>125706538</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495817</v>
+        <v>495769</v>
       </c>
       <c r="R33" t="n">
-        <v>6832682</v>
+        <v>6832671</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125706538</v>
+        <v>125708014</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495769</v>
+        <v>495817</v>
       </c>
       <c r="R34" t="n">
-        <v>6832671</v>
+        <v>6832682</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>125706445</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>125708314</v>
       </c>
       <c r="B36" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4115,57 +4115,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125707003</v>
+        <v>125706917</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495724</v>
+        <v>495776</v>
       </c>
       <c r="R37" t="n">
-        <v>6832599</v>
+        <v>6832649</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4209,22 +4200,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B38" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R38" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,10 +4309,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706947</v>
+        <v>125707384</v>
       </c>
       <c r="B39" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4329,21 +4320,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4353,13 +4344,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495763</v>
+        <v>495765</v>
       </c>
       <c r="R39" t="n">
-        <v>6832629</v>
+        <v>6832558</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4403,57 +4394,66 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707384</v>
+        <v>125707003</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495765</v>
+        <v>495724</v>
       </c>
       <c r="R40" t="n">
-        <v>6832558</v>
+        <v>6832599</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4515,7 +4515,7 @@
         <v>125706892</v>
       </c>
       <c r="B41" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,32 +4609,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125707372</v>
+        <v>125706691</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78997</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495764</v>
+        <v>495777</v>
       </c>
       <c r="R42" t="n">
-        <v>6832553</v>
+        <v>6832671</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4694,44 +4694,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125706691</v>
+        <v>125707372</v>
       </c>
       <c r="B43" t="n">
-        <v>78996</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495777</v>
+        <v>495764</v>
       </c>
       <c r="R43" t="n">
-        <v>6832671</v>
+        <v>6832553</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4791,12 +4791,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
         <v>125706714</v>
       </c>
       <c r="B44" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,48 +4909,63 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125706720</v>
+        <v>125707718</v>
       </c>
       <c r="B45" t="n">
-        <v>79004</v>
+        <v>56844</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495782</v>
+        <v>495818</v>
       </c>
       <c r="R45" t="n">
-        <v>6832661</v>
+        <v>6832436</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4994,60 +5009,54 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125707718</v>
+        <v>125708266</v>
       </c>
       <c r="B46" t="n">
-        <v>56843</v>
+        <v>98341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5056,13 +5065,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495818</v>
+        <v>495706</v>
       </c>
       <c r="R46" t="n">
-        <v>6832436</v>
+        <v>6832880</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5106,66 +5115,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B47" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R47" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5227,7 +5227,7 @@
         <v>125706842</v>
       </c>
       <c r="B48" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>125706827</v>
       </c>
       <c r="B49" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>125707108</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125708210</v>
+        <v>125708307</v>
       </c>
       <c r="B52" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495705</v>
+        <v>495712</v>
       </c>
       <c r="R52" t="n">
-        <v>6832884</v>
+        <v>6832874</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5706,44 +5706,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125706943</v>
+        <v>125707134</v>
       </c>
       <c r="B53" t="n">
-        <v>80075</v>
+        <v>56959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495715</v>
+        <v>495770</v>
       </c>
       <c r="R53" t="n">
-        <v>6832599</v>
+        <v>6832555</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5815,10 +5815,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125708307</v>
+        <v>125706764</v>
       </c>
       <c r="B54" t="n">
-        <v>80075</v>
+        <v>79005</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,21 +5826,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5850,13 +5850,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495712</v>
+        <v>495761</v>
       </c>
       <c r="R54" t="n">
-        <v>6832874</v>
+        <v>6832671</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5900,44 +5900,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125707134</v>
+        <v>125708210</v>
       </c>
       <c r="B55" t="n">
-        <v>56958</v>
+        <v>80076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495770</v>
+        <v>495705</v>
       </c>
       <c r="R55" t="n">
-        <v>6832555</v>
+        <v>6832884</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5997,22 +5997,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706764</v>
+        <v>125706943</v>
       </c>
       <c r="B56" t="n">
-        <v>79004</v>
+        <v>80076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6020,21 +6020,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6044,13 +6044,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495761</v>
+        <v>495715</v>
       </c>
       <c r="R56" t="n">
-        <v>6832671</v>
+        <v>6832599</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6094,12 +6094,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
         <v>125706779</v>
       </c>
       <c r="B57" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>125707479</v>
       </c>
       <c r="B58" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>125707413</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>125707093</v>
       </c>
       <c r="B60" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>125707370</v>
       </c>
       <c r="B62" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6715,48 +6715,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125706395</v>
+        <v>125707073</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495818</v>
+        <v>495738</v>
       </c>
       <c r="R63" t="n">
-        <v>6832725</v>
+        <v>6832601</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6812,57 +6821,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B64" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R64" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708583</v>
+        <v>125708074</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,34 +6929,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495841</v>
+        <v>495733</v>
       </c>
       <c r="R65" t="n">
-        <v>6833181</v>
+        <v>6832780</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125708074</v>
+        <v>125708596</v>
       </c>
       <c r="B66" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7050,13 +7050,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495733</v>
+        <v>495930</v>
       </c>
       <c r="R66" t="n">
-        <v>6832780</v>
+        <v>6833128</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7100,22 +7100,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125708596</v>
+        <v>125706873</v>
       </c>
       <c r="B67" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495930</v>
+        <v>495718</v>
       </c>
       <c r="R67" t="n">
-        <v>6833128</v>
+        <v>6832621</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7197,22 +7197,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125706873</v>
+        <v>125708583</v>
       </c>
       <c r="B68" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,34 +7220,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495718</v>
+        <v>495841</v>
       </c>
       <c r="R68" t="n">
-        <v>6832621</v>
+        <v>6833181</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125707048</v>
+        <v>125707544</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495746</v>
+        <v>495877</v>
       </c>
       <c r="R15" t="n">
-        <v>6832627</v>
+        <v>6832537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125707544</v>
+        <v>125707655</v>
       </c>
       <c r="B16" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495877</v>
+        <v>495798</v>
       </c>
       <c r="R16" t="n">
-        <v>6832537</v>
+        <v>6832444</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125707655</v>
+        <v>125707048</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495798</v>
+        <v>495746</v>
       </c>
       <c r="R17" t="n">
-        <v>6832444</v>
+        <v>6832627</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2224,12 +2224,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125706637</v>
+        <v>125706538</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495737</v>
+        <v>495769</v>
       </c>
       <c r="R29" t="n">
-        <v>6832680</v>
+        <v>6832671</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3406,22 +3406,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125708848</v>
+        <v>125708014</v>
       </c>
       <c r="B30" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495680</v>
+        <v>495817</v>
       </c>
       <c r="R30" t="n">
-        <v>6832870</v>
+        <v>6832682</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125706538</v>
+        <v>125706637</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495769</v>
+        <v>495737</v>
       </c>
       <c r="R33" t="n">
-        <v>6832671</v>
+        <v>6832680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3794,22 +3794,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125708014</v>
+        <v>125708848</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495817</v>
+        <v>495680</v>
       </c>
       <c r="R34" t="n">
-        <v>6832682</v>
+        <v>6832870</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4512,48 +4512,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125706892</v>
+        <v>125706714</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495711</v>
+        <v>495751</v>
       </c>
       <c r="R41" t="n">
-        <v>6832636</v>
+        <v>6832672</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4609,32 +4618,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125706691</v>
+        <v>125707372</v>
       </c>
       <c r="B42" t="n">
-        <v>78997</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,13 +4653,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495777</v>
+        <v>495764</v>
       </c>
       <c r="R42" t="n">
-        <v>6832671</v>
+        <v>6832553</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4694,22 +4703,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125707372</v>
+        <v>125706892</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4717,21 +4726,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4741,10 +4750,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495764</v>
+        <v>495711</v>
       </c>
       <c r="R43" t="n">
-        <v>6832553</v>
+        <v>6832636</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4803,54 +4812,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125706714</v>
+        <v>125706691</v>
       </c>
       <c r="B44" t="n">
-        <v>98341</v>
+        <v>78997</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495751</v>
+        <v>495777</v>
       </c>
       <c r="R44" t="n">
-        <v>6832672</v>
+        <v>6832671</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4897,60 +4897,54 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125707718</v>
+        <v>125708266</v>
       </c>
       <c r="B45" t="n">
-        <v>56844</v>
+        <v>98341</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4959,13 +4953,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495818</v>
+        <v>495706</v>
       </c>
       <c r="R45" t="n">
-        <v>6832436</v>
+        <v>6832880</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5009,66 +5003,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B46" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R46" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5127,48 +5112,63 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125706720</v>
+        <v>125707718</v>
       </c>
       <c r="B47" t="n">
-        <v>79005</v>
+        <v>56844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495782</v>
+        <v>495818</v>
       </c>
       <c r="R47" t="n">
-        <v>6832661</v>
+        <v>6832436</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5212,22 +5212,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125706842</v>
+        <v>125707108</v>
       </c>
       <c r="B48" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495760</v>
+        <v>495743</v>
       </c>
       <c r="R48" t="n">
-        <v>6832666</v>
+        <v>6832597</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,45 +5321,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125706827</v>
+        <v>125707720</v>
       </c>
       <c r="B49" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495745</v>
+        <v>495839</v>
       </c>
       <c r="R49" t="n">
-        <v>6832669</v>
+        <v>6832437</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5418,10 +5427,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125707108</v>
+        <v>125706842</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,21 +5438,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5453,10 +5462,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495743</v>
+        <v>495760</v>
       </c>
       <c r="R50" t="n">
-        <v>6832597</v>
+        <v>6832666</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5515,54 +5524,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125707720</v>
+        <v>125706827</v>
       </c>
       <c r="B51" t="n">
-        <v>98341</v>
+        <v>78731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495839</v>
+        <v>495745</v>
       </c>
       <c r="R51" t="n">
-        <v>6832437</v>
+        <v>6832669</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6415,45 +6415,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707093</v>
+        <v>125707493</v>
       </c>
       <c r="B60" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495727</v>
+        <v>495766</v>
       </c>
       <c r="R60" t="n">
-        <v>6832581</v>
+        <v>6832499</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6512,54 +6521,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125707493</v>
+        <v>125707093</v>
       </c>
       <c r="B61" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495766</v>
+        <v>495727</v>
       </c>
       <c r="R61" t="n">
-        <v>6832499</v>
+        <v>6832581</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>125706913</v>
       </c>
       <c r="B7" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125707511</v>
+        <v>125706635</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495780</v>
+        <v>495776</v>
       </c>
       <c r="R9" t="n">
-        <v>6832481</v>
+        <v>6832691</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125706635</v>
+        <v>125707511</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495776</v>
+        <v>495780</v>
       </c>
       <c r="R10" t="n">
-        <v>6832691</v>
+        <v>6832481</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1645,48 +1645,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125707173</v>
+        <v>125708132</v>
       </c>
       <c r="B12" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495761</v>
+        <v>495728</v>
       </c>
       <c r="R12" t="n">
-        <v>6832581</v>
+        <v>6832782</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,69 +1739,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125708132</v>
+        <v>125707173</v>
       </c>
       <c r="B13" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495728</v>
+        <v>495761</v>
       </c>
       <c r="R13" t="n">
-        <v>6832782</v>
+        <v>6832581</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>125707583</v>
       </c>
       <c r="B14" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125707544</v>
+        <v>125708856</v>
       </c>
       <c r="B15" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,37 +1956,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495877</v>
+        <v>495902</v>
       </c>
       <c r="R15" t="n">
-        <v>6832537</v>
+        <v>6833046</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2030,22 +2030,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125707655</v>
+        <v>125707048</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495798</v>
+        <v>495746</v>
       </c>
       <c r="R16" t="n">
-        <v>6832444</v>
+        <v>6832627</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125707048</v>
+        <v>125707655</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495746</v>
+        <v>495798</v>
       </c>
       <c r="R17" t="n">
-        <v>6832627</v>
+        <v>6832444</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2224,22 +2224,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125708856</v>
+        <v>125707544</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,37 +2247,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495902</v>
+        <v>495877</v>
       </c>
       <c r="R18" t="n">
-        <v>6833046</v>
+        <v>6832537</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2321,12 +2321,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
         <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125706777</v>
+        <v>125706788</v>
       </c>
       <c r="B23" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495767</v>
+        <v>495756</v>
       </c>
       <c r="R23" t="n">
-        <v>6832677</v>
+        <v>6832675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125706788</v>
+        <v>125706777</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495756</v>
+        <v>495767</v>
       </c>
       <c r="R25" t="n">
-        <v>6832675</v>
+        <v>6832677</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3024,7 +3024,7 @@
         <v>125707033</v>
       </c>
       <c r="B26" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125706538</v>
+        <v>125708014</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495769</v>
+        <v>495817</v>
       </c>
       <c r="R29" t="n">
-        <v>6832671</v>
+        <v>6832682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125708014</v>
+        <v>125706538</v>
       </c>
       <c r="B30" t="n">
         <v>78973</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495817</v>
+        <v>495769</v>
       </c>
       <c r="R30" t="n">
-        <v>6832682</v>
+        <v>6832671</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125707016</v>
+        <v>125706637</v>
       </c>
       <c r="B31" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,21 +3526,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3550,13 +3550,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495749</v>
+        <v>495737</v>
       </c>
       <c r="R31" t="n">
-        <v>6832629</v>
+        <v>6832680</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3600,22 +3600,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125707083</v>
+        <v>125708848</v>
       </c>
       <c r="B32" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495751</v>
+        <v>495680</v>
       </c>
       <c r="R32" t="n">
-        <v>6832612</v>
+        <v>6832870</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125706637</v>
+        <v>125707016</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495737</v>
+        <v>495749</v>
       </c>
       <c r="R33" t="n">
-        <v>6832680</v>
+        <v>6832629</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3794,22 +3794,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125708848</v>
+        <v>125707083</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495680</v>
+        <v>495751</v>
       </c>
       <c r="R34" t="n">
-        <v>6832870</v>
+        <v>6832612</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125706445</v>
+        <v>125708314</v>
       </c>
       <c r="B35" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495778</v>
+        <v>495700</v>
       </c>
       <c r="R35" t="n">
-        <v>6832690</v>
+        <v>6832875</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125708314</v>
+        <v>125706445</v>
       </c>
       <c r="B36" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495700</v>
+        <v>495778</v>
       </c>
       <c r="R36" t="n">
-        <v>6832875</v>
+        <v>6832690</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,7 +4115,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B37" t="n">
         <v>79005</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R37" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4212,7 +4212,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706947</v>
+        <v>125706917</v>
       </c>
       <c r="B38" t="n">
         <v>79005</v>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495763</v>
+        <v>495776</v>
       </c>
       <c r="R38" t="n">
-        <v>6832629</v>
+        <v>6832649</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,45 +4309,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125707384</v>
+        <v>125707003</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495765</v>
+        <v>495724</v>
       </c>
       <c r="R39" t="n">
-        <v>6832558</v>
+        <v>6832599</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4406,54 +4415,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707003</v>
+        <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495724</v>
+        <v>495765</v>
       </c>
       <c r="R40" t="n">
-        <v>6832599</v>
+        <v>6832558</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4512,57 +4512,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125706714</v>
+        <v>125706892</v>
       </c>
       <c r="B41" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495751</v>
+        <v>495711</v>
       </c>
       <c r="R41" t="n">
-        <v>6832672</v>
+        <v>6832636</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4618,32 +4609,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125707372</v>
+        <v>125706691</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78997</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4653,13 +4644,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495764</v>
+        <v>495777</v>
       </c>
       <c r="R42" t="n">
-        <v>6832553</v>
+        <v>6832671</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4703,22 +4694,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125706892</v>
+        <v>125707372</v>
       </c>
       <c r="B43" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4726,21 +4717,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4750,10 +4741,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495711</v>
+        <v>495764</v>
       </c>
       <c r="R43" t="n">
-        <v>6832636</v>
+        <v>6832553</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4812,45 +4803,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125706691</v>
+        <v>125706714</v>
       </c>
       <c r="B44" t="n">
-        <v>78997</v>
+        <v>98343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495777</v>
+        <v>495751</v>
       </c>
       <c r="R44" t="n">
-        <v>6832671</v>
+        <v>6832672</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4897,66 +4897,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B45" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R45" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5015,48 +5006,63 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125706720</v>
+        <v>125707718</v>
       </c>
       <c r="B46" t="n">
-        <v>79005</v>
+        <v>56844</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495782</v>
+        <v>495818</v>
       </c>
       <c r="R46" t="n">
-        <v>6832661</v>
+        <v>6832436</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5100,60 +5106,54 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125707718</v>
+        <v>125708266</v>
       </c>
       <c r="B47" t="n">
-        <v>56844</v>
+        <v>98343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495818</v>
+        <v>495706</v>
       </c>
       <c r="R47" t="n">
-        <v>6832436</v>
+        <v>6832880</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5212,22 +5212,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125707108</v>
+        <v>125706827</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495743</v>
+        <v>495745</v>
       </c>
       <c r="R48" t="n">
-        <v>6832597</v>
+        <v>6832669</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,54 +5321,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125707720</v>
+        <v>125706842</v>
       </c>
       <c r="B49" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495839</v>
+        <v>495760</v>
       </c>
       <c r="R49" t="n">
-        <v>6832437</v>
+        <v>6832666</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,10 +5418,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125706842</v>
+        <v>125707108</v>
       </c>
       <c r="B50" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5438,21 +5429,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5462,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495760</v>
+        <v>495743</v>
       </c>
       <c r="R50" t="n">
-        <v>6832666</v>
+        <v>6832597</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5524,45 +5515,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125706827</v>
+        <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>98343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495745</v>
+        <v>495839</v>
       </c>
       <c r="R51" t="n">
-        <v>6832669</v>
+        <v>6832437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,32 +5621,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125708307</v>
+        <v>125707134</v>
       </c>
       <c r="B52" t="n">
-        <v>80076</v>
+        <v>56959</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495712</v>
+        <v>495770</v>
       </c>
       <c r="R52" t="n">
-        <v>6832874</v>
+        <v>6832555</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5718,32 +5718,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125707134</v>
+        <v>125708210</v>
       </c>
       <c r="B53" t="n">
-        <v>56959</v>
+        <v>80076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5753,13 +5753,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495770</v>
+        <v>495705</v>
       </c>
       <c r="R53" t="n">
-        <v>6832555</v>
+        <v>6832884</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5803,22 +5803,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706764</v>
+        <v>125706943</v>
       </c>
       <c r="B54" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,21 +5826,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5850,13 +5850,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495761</v>
+        <v>495715</v>
       </c>
       <c r="R54" t="n">
-        <v>6832671</v>
+        <v>6832599</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5900,19 +5900,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708210</v>
+        <v>125708307</v>
       </c>
       <c r="B55" t="n">
         <v>80076</v>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495705</v>
+        <v>495712</v>
       </c>
       <c r="R55" t="n">
-        <v>6832884</v>
+        <v>6832874</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5997,22 +5997,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706943</v>
+        <v>125706764</v>
       </c>
       <c r="B56" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6020,21 +6020,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6044,13 +6044,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495715</v>
+        <v>495761</v>
       </c>
       <c r="R56" t="n">
-        <v>6832599</v>
+        <v>6832671</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6094,12 +6094,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
         <v>125706779</v>
       </c>
       <c r="B57" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>125707479</v>
       </c>
       <c r="B58" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125707413</v>
+        <v>125707093</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495782</v>
+        <v>495727</v>
       </c>
       <c r="R59" t="n">
-        <v>6832513</v>
+        <v>6832581</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6415,54 +6415,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707493</v>
+        <v>125707413</v>
       </c>
       <c r="B60" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495766</v>
+        <v>495782</v>
       </c>
       <c r="R60" t="n">
-        <v>6832499</v>
+        <v>6832513</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6521,45 +6512,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125707093</v>
+        <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495727</v>
+        <v>495766</v>
       </c>
       <c r="R61" t="n">
-        <v>6832581</v>
+        <v>6832499</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125707370</v>
+        <v>125706395</v>
       </c>
       <c r="B62" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495793</v>
+        <v>495818</v>
       </c>
       <c r="R62" t="n">
-        <v>6832568</v>
+        <v>6832725</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,69 +6703,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125707073</v>
+        <v>125707370</v>
       </c>
       <c r="B63" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495738</v>
+        <v>495793</v>
       </c>
       <c r="R63" t="n">
-        <v>6832601</v>
+        <v>6832568</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6809,60 +6800,69 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125706395</v>
+        <v>125707073</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495818</v>
+        <v>495738</v>
       </c>
       <c r="R64" t="n">
-        <v>6832725</v>
+        <v>6832601</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125706524</v>
+        <v>125707173</v>
       </c>
       <c r="B11" t="n">
         <v>79005</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495786</v>
+        <v>495761</v>
       </c>
       <c r="R11" t="n">
-        <v>6832670</v>
+        <v>6832581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,57 +1645,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125708132</v>
+        <v>125706524</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495728</v>
+        <v>495786</v>
       </c>
       <c r="R12" t="n">
-        <v>6832782</v>
+        <v>6832670</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1739,60 +1730,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125707173</v>
+        <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495761</v>
+        <v>495728</v>
       </c>
       <c r="R13" t="n">
-        <v>6832581</v>
+        <v>6832782</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2430,57 +2430,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125708060</v>
+        <v>125706678</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495753</v>
+        <v>495780</v>
       </c>
       <c r="R20" t="n">
-        <v>6832752</v>
+        <v>6832667</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2524,60 +2515,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125706678</v>
+        <v>125708060</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495780</v>
+        <v>495753</v>
       </c>
       <c r="R21" t="n">
-        <v>6832667</v>
+        <v>6832752</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2621,12 +2621,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3709,45 +3709,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125707016</v>
+        <v>125706445</v>
       </c>
       <c r="B33" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495749</v>
+        <v>495778</v>
       </c>
       <c r="R33" t="n">
-        <v>6832629</v>
+        <v>6832690</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125707083</v>
+        <v>125707016</v>
       </c>
       <c r="B34" t="n">
         <v>79005</v>
@@ -3841,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495751</v>
+        <v>495749</v>
       </c>
       <c r="R34" t="n">
-        <v>6832612</v>
+        <v>6832629</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3903,54 +3912,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125708314</v>
+        <v>125707083</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495700</v>
+        <v>495751</v>
       </c>
       <c r="R35" t="n">
-        <v>6832875</v>
+        <v>6832612</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125706445</v>
+        <v>125708314</v>
       </c>
       <c r="B36" t="n">
         <v>98343</v>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495778</v>
+        <v>495700</v>
       </c>
       <c r="R36" t="n">
-        <v>6832690</v>
+        <v>6832875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125706827</v>
+        <v>125706842</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>79005</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495745</v>
+        <v>495760</v>
       </c>
       <c r="R48" t="n">
-        <v>6832669</v>
+        <v>6832666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125706842</v>
+        <v>125707108</v>
       </c>
       <c r="B49" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5332,21 +5332,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495760</v>
+        <v>495743</v>
       </c>
       <c r="R49" t="n">
-        <v>6832666</v>
+        <v>6832597</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5418,10 +5418,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125707108</v>
+        <v>125706827</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,21 +5429,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495743</v>
+        <v>495745</v>
       </c>
       <c r="R50" t="n">
-        <v>6832597</v>
+        <v>6832669</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5621,32 +5621,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125707134</v>
+        <v>125706764</v>
       </c>
       <c r="B52" t="n">
-        <v>56959</v>
+        <v>79005</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100065</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495770</v>
+        <v>495761</v>
       </c>
       <c r="R52" t="n">
-        <v>6832555</v>
+        <v>6832671</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5706,60 +5706,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125708210</v>
+        <v>125706779</v>
       </c>
       <c r="B53" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495705</v>
+        <v>495724</v>
       </c>
       <c r="R53" t="n">
-        <v>6832884</v>
+        <v>6832662</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5803,57 +5812,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706943</v>
+        <v>125707479</v>
       </c>
       <c r="B54" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495715</v>
+        <v>495776</v>
       </c>
       <c r="R54" t="n">
-        <v>6832599</v>
+        <v>6832485</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5912,7 +5930,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708307</v>
+        <v>125708210</v>
       </c>
       <c r="B55" t="n">
         <v>80076</v>
@@ -5947,13 +5965,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495712</v>
+        <v>495705</v>
       </c>
       <c r="R55" t="n">
-        <v>6832874</v>
+        <v>6832884</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5997,22 +6015,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706764</v>
+        <v>125706943</v>
       </c>
       <c r="B56" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6020,21 +6038,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6044,13 +6062,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495761</v>
+        <v>495715</v>
       </c>
       <c r="R56" t="n">
-        <v>6832671</v>
+        <v>6832599</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6094,66 +6112,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125706779</v>
+        <v>125708307</v>
       </c>
       <c r="B57" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495724</v>
+        <v>495712</v>
       </c>
       <c r="R57" t="n">
-        <v>6832662</v>
+        <v>6832874</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6212,54 +6221,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125707479</v>
+        <v>125707134</v>
       </c>
       <c r="B58" t="n">
-        <v>98343</v>
+        <v>56959</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495776</v>
+        <v>495770</v>
       </c>
       <c r="R58" t="n">
-        <v>6832485</v>
+        <v>6832555</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R62" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,22 +6703,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125707370</v>
+        <v>125706395</v>
       </c>
       <c r="B63" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495793</v>
+        <v>495818</v>
       </c>
       <c r="R63" t="n">
-        <v>6832568</v>
+        <v>6832725</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6800,12 +6800,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125708078</v>
+        <v>125707087</v>
       </c>
       <c r="B2" t="n">
         <v>78973</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495734</v>
+        <v>495739</v>
       </c>
       <c r="R2" t="n">
-        <v>6832790</v>
+        <v>6832585</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125707087</v>
+        <v>125708078</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495739</v>
+        <v>495734</v>
       </c>
       <c r="R3" t="n">
-        <v>6832585</v>
+        <v>6832790</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125707417</v>
+        <v>125706872</v>
       </c>
       <c r="B4" t="n">
-        <v>79591</v>
+        <v>79005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495819</v>
+        <v>495765</v>
       </c>
       <c r="R4" t="n">
-        <v>6832571</v>
+        <v>6832663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706791</v>
+        <v>125706913</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495730</v>
+        <v>495727</v>
       </c>
       <c r="R5" t="n">
-        <v>6832652</v>
+        <v>6832609</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125706913</v>
+        <v>125706791</v>
       </c>
       <c r="B7" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495727</v>
+        <v>495730</v>
       </c>
       <c r="R7" t="n">
-        <v>6832609</v>
+        <v>6832652</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125706872</v>
+        <v>125707417</v>
       </c>
       <c r="B8" t="n">
-        <v>79005</v>
+        <v>79591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495765</v>
+        <v>495819</v>
       </c>
       <c r="R8" t="n">
-        <v>6832663</v>
+        <v>6832571</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125706635</v>
+        <v>125706524</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495776</v>
+        <v>495786</v>
       </c>
       <c r="R9" t="n">
-        <v>6832691</v>
+        <v>6832670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125707511</v>
+        <v>125707173</v>
       </c>
       <c r="B10" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495780</v>
+        <v>495761</v>
       </c>
       <c r="R10" t="n">
-        <v>6832481</v>
+        <v>6832581</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125707173</v>
+        <v>125706635</v>
       </c>
       <c r="B11" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495761</v>
+        <v>495776</v>
       </c>
       <c r="R11" t="n">
-        <v>6832581</v>
+        <v>6832691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125706524</v>
+        <v>125707511</v>
       </c>
       <c r="B12" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495786</v>
+        <v>495780</v>
       </c>
       <c r="R12" t="n">
-        <v>6832670</v>
+        <v>6832481</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
         <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>125707583</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125708856</v>
+        <v>125707048</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1976,17 +1976,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495902</v>
+        <v>495746</v>
       </c>
       <c r="R15" t="n">
-        <v>6833046</v>
+        <v>6832627</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2030,22 +2030,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125707048</v>
+        <v>125707655</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495746</v>
+        <v>495798</v>
       </c>
       <c r="R16" t="n">
-        <v>6832627</v>
+        <v>6832444</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125707655</v>
+        <v>125708856</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,34 +2150,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495798</v>
+        <v>495902</v>
       </c>
       <c r="R17" t="n">
-        <v>6832444</v>
+        <v>6833046</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2430,48 +2430,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125706678</v>
+        <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495780</v>
+        <v>495753</v>
       </c>
       <c r="R20" t="n">
-        <v>6832667</v>
+        <v>6832752</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2515,69 +2524,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125708060</v>
+        <v>125706678</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495753</v>
+        <v>495780</v>
       </c>
       <c r="R21" t="n">
-        <v>6832752</v>
+        <v>6832667</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2621,12 +2621,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2827,45 +2827,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125707543</v>
+        <v>125707033</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495772</v>
+        <v>495733</v>
       </c>
       <c r="R24" t="n">
-        <v>6832482</v>
+        <v>6832598</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,54 +3030,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125707033</v>
+        <v>125707543</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495733</v>
+        <v>495772</v>
       </c>
       <c r="R26" t="n">
-        <v>6832598</v>
+        <v>6832482</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3227,7 +3227,7 @@
         <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,45 +3321,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125708014</v>
+        <v>125708314</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495817</v>
+        <v>495700</v>
       </c>
       <c r="R29" t="n">
-        <v>6832682</v>
+        <v>6832875</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,45 +3427,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125706538</v>
+        <v>125706445</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495769</v>
+        <v>495778</v>
       </c>
       <c r="R30" t="n">
-        <v>6832671</v>
+        <v>6832690</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,10 +3533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125706637</v>
+        <v>125707083</v>
       </c>
       <c r="B31" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,21 +3544,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3550,13 +3568,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495737</v>
+        <v>495751</v>
       </c>
       <c r="R31" t="n">
-        <v>6832680</v>
+        <v>6832612</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3600,22 +3618,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125708848</v>
+        <v>125707016</v>
       </c>
       <c r="B32" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3623,21 +3641,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3647,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495680</v>
+        <v>495749</v>
       </c>
       <c r="R32" t="n">
-        <v>6832870</v>
+        <v>6832629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,54 +3727,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125706445</v>
+        <v>125708014</v>
       </c>
       <c r="B33" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495778</v>
+        <v>495817</v>
       </c>
       <c r="R33" t="n">
-        <v>6832690</v>
+        <v>6832682</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3815,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125707016</v>
+        <v>125706538</v>
       </c>
       <c r="B34" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3826,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3850,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495749</v>
+        <v>495769</v>
       </c>
       <c r="R34" t="n">
-        <v>6832629</v>
+        <v>6832671</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,10 +3921,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125707083</v>
+        <v>125706637</v>
       </c>
       <c r="B35" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3923,21 +3932,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3947,13 +3956,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495751</v>
+        <v>495737</v>
       </c>
       <c r="R35" t="n">
-        <v>6832612</v>
+        <v>6832680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3997,66 +4006,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125708314</v>
+        <v>125708848</v>
       </c>
       <c r="B36" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495700</v>
+        <v>495680</v>
       </c>
       <c r="R36" t="n">
-        <v>6832875</v>
+        <v>6832870</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,10 +4115,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125706947</v>
+        <v>125707384</v>
       </c>
       <c r="B37" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4126,21 +4126,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495763</v>
+        <v>495765</v>
       </c>
       <c r="R37" t="n">
-        <v>6832629</v>
+        <v>6832558</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4200,12 +4200,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4309,57 +4309,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125707003</v>
+        <v>125706947</v>
       </c>
       <c r="B39" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495724</v>
+        <v>495763</v>
       </c>
       <c r="R39" t="n">
-        <v>6832599</v>
+        <v>6832629</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4403,57 +4394,66 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707384</v>
+        <v>125707003</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495765</v>
+        <v>495724</v>
       </c>
       <c r="R40" t="n">
-        <v>6832558</v>
+        <v>6832599</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4512,32 +4512,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125706892</v>
+        <v>125706691</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>78997</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495711</v>
+        <v>495777</v>
       </c>
       <c r="R41" t="n">
-        <v>6832636</v>
+        <v>6832671</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4597,44 +4597,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125706691</v>
+        <v>125706892</v>
       </c>
       <c r="B42" t="n">
-        <v>78997</v>
+        <v>80076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495777</v>
+        <v>495711</v>
       </c>
       <c r="R42" t="n">
-        <v>6832671</v>
+        <v>6832636</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4694,12 +4694,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
         <v>125706714</v>
       </c>
       <c r="B44" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>125708266</v>
       </c>
       <c r="B47" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125706764</v>
+        <v>125708210</v>
       </c>
       <c r="B52" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495761</v>
+        <v>495705</v>
       </c>
       <c r="R52" t="n">
-        <v>6832671</v>
+        <v>6832884</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5718,54 +5718,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125706779</v>
+        <v>125706943</v>
       </c>
       <c r="B53" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495724</v>
+        <v>495715</v>
       </c>
       <c r="R53" t="n">
-        <v>6832662</v>
+        <v>6832599</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5824,54 +5815,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125707479</v>
+        <v>125708307</v>
       </c>
       <c r="B54" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495776</v>
+        <v>495712</v>
       </c>
       <c r="R54" t="n">
-        <v>6832485</v>
+        <v>6832874</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5930,48 +5912,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708210</v>
+        <v>125707479</v>
       </c>
       <c r="B55" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495705</v>
+        <v>495776</v>
       </c>
       <c r="R55" t="n">
-        <v>6832884</v>
+        <v>6832485</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6015,57 +6006,66 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706943</v>
+        <v>125706779</v>
       </c>
       <c r="B56" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495715</v>
+        <v>495724</v>
       </c>
       <c r="R56" t="n">
-        <v>6832599</v>
+        <v>6832662</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6124,10 +6124,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125708307</v>
+        <v>125706764</v>
       </c>
       <c r="B57" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6135,21 +6135,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495712</v>
+        <v>495761</v>
       </c>
       <c r="R57" t="n">
-        <v>6832874</v>
+        <v>6832671</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6209,12 +6209,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125707093</v>
+        <v>125707413</v>
       </c>
       <c r="B59" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495727</v>
+        <v>495782</v>
       </c>
       <c r="R59" t="n">
-        <v>6832581</v>
+        <v>6832513</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707413</v>
+        <v>125707093</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6426,21 +6426,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495782</v>
+        <v>495727</v>
       </c>
       <c r="R60" t="n">
-        <v>6832513</v>
+        <v>6832581</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6515,7 +6515,7 @@
         <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,48 +6618,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125707370</v>
+        <v>125707073</v>
       </c>
       <c r="B62" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495793</v>
+        <v>495738</v>
       </c>
       <c r="R62" t="n">
-        <v>6832568</v>
+        <v>6832601</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6703,22 +6712,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6735,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R63" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6800,69 +6809,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B64" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R64" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -2730,48 +2730,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125706788</v>
+        <v>125707033</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495756</v>
+        <v>495733</v>
       </c>
       <c r="R23" t="n">
-        <v>6832675</v>
+        <v>6832598</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2815,69 +2824,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125707033</v>
+        <v>125706777</v>
       </c>
       <c r="B24" t="n">
-        <v>98345</v>
+        <v>79005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495733</v>
+        <v>495767</v>
       </c>
       <c r="R24" t="n">
-        <v>6832598</v>
+        <v>6832677</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2921,22 +2921,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125706777</v>
+        <v>125706788</v>
       </c>
       <c r="B25" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495767</v>
+        <v>495756</v>
       </c>
       <c r="R25" t="n">
-        <v>6832677</v>
+        <v>6832675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,54 +3321,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125708314</v>
+        <v>125707083</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>79005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495700</v>
+        <v>495751</v>
       </c>
       <c r="R29" t="n">
-        <v>6832875</v>
+        <v>6832612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,54 +3418,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125706445</v>
+        <v>125707016</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>79005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495778</v>
+        <v>495749</v>
       </c>
       <c r="R30" t="n">
-        <v>6832690</v>
+        <v>6832629</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125707083</v>
+        <v>125708014</v>
       </c>
       <c r="B31" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,21 +3526,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3550,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495751</v>
+        <v>495817</v>
       </c>
       <c r="R31" t="n">
-        <v>6832612</v>
+        <v>6832682</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,10 +3612,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125707016</v>
+        <v>125706538</v>
       </c>
       <c r="B32" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,21 +3623,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495749</v>
+        <v>495769</v>
       </c>
       <c r="R32" t="n">
-        <v>6832629</v>
+        <v>6832671</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,10 +3709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125708014</v>
+        <v>125706637</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3720,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,13 +3744,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495817</v>
+        <v>495737</v>
       </c>
       <c r="R33" t="n">
-        <v>6832682</v>
+        <v>6832680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3812,22 +3794,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125706538</v>
+        <v>125708848</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3817,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495769</v>
+        <v>495680</v>
       </c>
       <c r="R34" t="n">
-        <v>6832671</v>
+        <v>6832870</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,48 +3903,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125706637</v>
+        <v>125708314</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495737</v>
+        <v>495700</v>
       </c>
       <c r="R35" t="n">
-        <v>6832680</v>
+        <v>6832875</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4006,57 +3997,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125708848</v>
+        <v>125706445</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495680</v>
+        <v>495778</v>
       </c>
       <c r="R36" t="n">
-        <v>6832870</v>
+        <v>6832690</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4909,45 +4909,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125706720</v>
+        <v>125708266</v>
       </c>
       <c r="B45" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495782</v>
+        <v>495706</v>
       </c>
       <c r="R45" t="n">
-        <v>6832661</v>
+        <v>6832880</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5118,54 +5127,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B47" t="n">
-        <v>98345</v>
+        <v>79005</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R47" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6618,57 +6618,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B62" t="n">
-        <v>98345</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R62" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6724,48 +6715,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125707370</v>
+        <v>125707073</v>
       </c>
       <c r="B63" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495793</v>
+        <v>495738</v>
       </c>
       <c r="R63" t="n">
-        <v>6832568</v>
+        <v>6832601</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6809,22 +6809,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R64" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,22 +6906,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708074</v>
+        <v>125708583</v>
       </c>
       <c r="B65" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,34 +6929,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495733</v>
+        <v>495841</v>
       </c>
       <c r="R65" t="n">
-        <v>6832780</v>
+        <v>6833181</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7015,7 +7015,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125708596</v>
+        <v>125708074</v>
       </c>
       <c r="B66" t="n">
         <v>80076</v>
@@ -7050,13 +7050,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495930</v>
+        <v>495733</v>
       </c>
       <c r="R66" t="n">
-        <v>6833128</v>
+        <v>6832780</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7100,19 +7100,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125706873</v>
+        <v>125708596</v>
       </c>
       <c r="B67" t="n">
         <v>80076</v>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495718</v>
+        <v>495930</v>
       </c>
       <c r="R67" t="n">
-        <v>6832621</v>
+        <v>6833128</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7197,22 +7197,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125708583</v>
+        <v>125706873</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,34 +7220,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495841</v>
+        <v>495718</v>
       </c>
       <c r="R68" t="n">
-        <v>6833181</v>
+        <v>6832621</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125707087</v>
+        <v>125708078</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495739</v>
+        <v>495734</v>
       </c>
       <c r="R2" t="n">
-        <v>6832585</v>
+        <v>6832790</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125708078</v>
+        <v>125707087</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495734</v>
+        <v>495739</v>
       </c>
       <c r="R3" t="n">
-        <v>6832790</v>
+        <v>6832585</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125706872</v>
+        <v>125708227</v>
       </c>
       <c r="B4" t="n">
-        <v>79005</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495765</v>
+        <v>495692</v>
       </c>
       <c r="R4" t="n">
-        <v>6832663</v>
+        <v>6832878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706913</v>
+        <v>125706872</v>
       </c>
       <c r="B5" t="n">
-        <v>92528</v>
+        <v>79009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495727</v>
+        <v>495765</v>
       </c>
       <c r="R5" t="n">
-        <v>6832609</v>
+        <v>6832663</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125708227</v>
+        <v>125706791</v>
       </c>
       <c r="B6" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495692</v>
+        <v>495730</v>
       </c>
       <c r="R6" t="n">
-        <v>6832878</v>
+        <v>6832652</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125706791</v>
+        <v>125706913</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495730</v>
+        <v>495727</v>
       </c>
       <c r="R7" t="n">
-        <v>6832652</v>
+        <v>6832609</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
         <v>125707417</v>
       </c>
       <c r="B8" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125706524</v>
       </c>
       <c r="B9" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125707173</v>
       </c>
       <c r="B10" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125706635</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125707511</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>125707583</v>
       </c>
       <c r="B14" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125707048</v>
+        <v>125707544</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495746</v>
+        <v>495877</v>
       </c>
       <c r="R15" t="n">
-        <v>6832627</v>
+        <v>6832537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
         <v>125707655</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>125708856</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125707544</v>
+        <v>125707048</v>
       </c>
       <c r="B18" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495877</v>
+        <v>495746</v>
       </c>
       <c r="R18" t="n">
-        <v>6832537</v>
+        <v>6832627</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
         <v>125708470</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>125706678</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>125706549</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,57 +2730,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125707033</v>
+        <v>125706788</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495733</v>
+        <v>495756</v>
       </c>
       <c r="R23" t="n">
-        <v>6832598</v>
+        <v>6832675</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2824,12 +2815,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2839,7 +2830,7 @@
         <v>125706777</v>
       </c>
       <c r="B24" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2933,10 +2924,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125706788</v>
+        <v>125707543</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2935,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,13 +2959,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495756</v>
+        <v>495772</v>
       </c>
       <c r="R25" t="n">
-        <v>6832675</v>
+        <v>6832482</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3018,57 +3009,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125707543</v>
+        <v>125707033</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495772</v>
+        <v>495733</v>
       </c>
       <c r="R26" t="n">
-        <v>6832482</v>
+        <v>6832598</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3130,7 +3130,7 @@
         <v>125706487</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,45 +3321,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125707083</v>
+        <v>125706445</v>
       </c>
       <c r="B29" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495751</v>
+        <v>495778</v>
       </c>
       <c r="R29" t="n">
-        <v>6832612</v>
+        <v>6832690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,45 +3427,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125707016</v>
+        <v>125708314</v>
       </c>
       <c r="B30" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495749</v>
+        <v>495700</v>
       </c>
       <c r="R30" t="n">
-        <v>6832629</v>
+        <v>6832875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,10 +3533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125708014</v>
+        <v>125707016</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,21 +3544,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3550,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495817</v>
+        <v>495749</v>
       </c>
       <c r="R31" t="n">
-        <v>6832682</v>
+        <v>6832629</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3612,10 +3630,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125706538</v>
+        <v>125707083</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3623,21 +3641,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3647,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495769</v>
+        <v>495751</v>
       </c>
       <c r="R32" t="n">
-        <v>6832671</v>
+        <v>6832612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3712,7 +3730,7 @@
         <v>125706637</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,7 +3827,7 @@
         <v>125708848</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3903,54 +3921,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125708314</v>
+        <v>125708014</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495700</v>
+        <v>495817</v>
       </c>
       <c r="R35" t="n">
-        <v>6832875</v>
+        <v>6832682</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,54 +4018,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125706445</v>
+        <v>125706538</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495778</v>
+        <v>495769</v>
       </c>
       <c r="R36" t="n">
-        <v>6832690</v>
+        <v>6832671</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,10 +4115,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125707384</v>
+        <v>125706917</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4126,21 +4126,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495765</v>
+        <v>495776</v>
       </c>
       <c r="R37" t="n">
-        <v>6832558</v>
+        <v>6832649</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4200,22 +4200,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706917</v>
+        <v>125706947</v>
       </c>
       <c r="B38" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495776</v>
+        <v>495763</v>
       </c>
       <c r="R38" t="n">
-        <v>6832649</v>
+        <v>6832629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,10 +4309,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125706947</v>
+        <v>125707384</v>
       </c>
       <c r="B39" t="n">
-        <v>79005</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4320,21 +4320,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,13 +4344,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495763</v>
+        <v>495765</v>
       </c>
       <c r="R39" t="n">
-        <v>6832629</v>
+        <v>6832558</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4394,12 +4394,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4409,7 +4409,7 @@
         <v>125707003</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,45 +4512,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125706691</v>
+        <v>125706714</v>
       </c>
       <c r="B41" t="n">
-        <v>78997</v>
+        <v>98349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495777</v>
+        <v>495751</v>
       </c>
       <c r="R41" t="n">
-        <v>6832671</v>
+        <v>6832672</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4597,22 +4606,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125706892</v>
+        <v>125707372</v>
       </c>
       <c r="B42" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4620,21 +4629,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4644,10 +4653,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495711</v>
+        <v>495764</v>
       </c>
       <c r="R42" t="n">
-        <v>6832636</v>
+        <v>6832553</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4706,32 +4715,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125707372</v>
+        <v>125706691</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>79001</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4741,13 +4750,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495764</v>
+        <v>495777</v>
       </c>
       <c r="R43" t="n">
-        <v>6832553</v>
+        <v>6832671</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4791,69 +4800,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125706714</v>
+        <v>125706892</v>
       </c>
       <c r="B44" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495751</v>
+        <v>495711</v>
       </c>
       <c r="R44" t="n">
-        <v>6832672</v>
+        <v>6832636</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4909,54 +4909,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B45" t="n">
-        <v>98345</v>
+        <v>79009</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R45" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5018,7 +5009,7 @@
         <v>125707718</v>
       </c>
       <c r="B46" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5127,45 +5118,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125706720</v>
+        <v>125708266</v>
       </c>
       <c r="B47" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495782</v>
+        <v>495706</v>
       </c>
       <c r="R47" t="n">
-        <v>6832661</v>
+        <v>6832880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5227,7 +5227,7 @@
         <v>125706842</v>
       </c>
       <c r="B48" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125707108</v>
+        <v>125706827</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5332,21 +5332,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495743</v>
+        <v>495745</v>
       </c>
       <c r="R49" t="n">
-        <v>6832597</v>
+        <v>6832669</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5418,10 +5418,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125706827</v>
+        <v>125707108</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,21 +5429,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495745</v>
+        <v>495743</v>
       </c>
       <c r="R50" t="n">
-        <v>6832669</v>
+        <v>6832597</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125708210</v>
+        <v>125706764</v>
       </c>
       <c r="B52" t="n">
-        <v>80076</v>
+        <v>79009</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495705</v>
+        <v>495761</v>
       </c>
       <c r="R52" t="n">
-        <v>6832884</v>
+        <v>6832671</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5718,32 +5718,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125706943</v>
+        <v>125707134</v>
       </c>
       <c r="B53" t="n">
-        <v>80076</v>
+        <v>56963</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495715</v>
+        <v>495770</v>
       </c>
       <c r="R53" t="n">
-        <v>6832599</v>
+        <v>6832555</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5815,10 +5815,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125708307</v>
+        <v>125708210</v>
       </c>
       <c r="B54" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5850,13 +5850,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495712</v>
+        <v>495705</v>
       </c>
       <c r="R54" t="n">
-        <v>6832874</v>
+        <v>6832884</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5900,66 +5900,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125707479</v>
+        <v>125706943</v>
       </c>
       <c r="B55" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495776</v>
+        <v>495715</v>
       </c>
       <c r="R55" t="n">
-        <v>6832485</v>
+        <v>6832599</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6018,54 +6009,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125706779</v>
+        <v>125708307</v>
       </c>
       <c r="B56" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495724</v>
+        <v>495712</v>
       </c>
       <c r="R56" t="n">
-        <v>6832662</v>
+        <v>6832874</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6124,48 +6106,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125706764</v>
+        <v>125706779</v>
       </c>
       <c r="B57" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495761</v>
+        <v>495724</v>
       </c>
       <c r="R57" t="n">
-        <v>6832671</v>
+        <v>6832662</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6209,57 +6200,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125707134</v>
+        <v>125707479</v>
       </c>
       <c r="B58" t="n">
-        <v>56959</v>
+        <v>98349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495770</v>
+        <v>495776</v>
       </c>
       <c r="R58" t="n">
-        <v>6832555</v>
+        <v>6832485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6321,7 +6321,7 @@
         <v>125707413</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,45 +6415,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707093</v>
+        <v>125707493</v>
       </c>
       <c r="B60" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495727</v>
+        <v>495766</v>
       </c>
       <c r="R60" t="n">
-        <v>6832581</v>
+        <v>6832499</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6512,54 +6521,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125707493</v>
+        <v>125707093</v>
       </c>
       <c r="B61" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495766</v>
+        <v>495727</v>
       </c>
       <c r="R61" t="n">
-        <v>6832499</v>
+        <v>6832581</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R62" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,69 +6703,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B63" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R63" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6821,48 +6812,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707370</v>
+        <v>125707073</v>
       </c>
       <c r="B64" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495793</v>
+        <v>495738</v>
       </c>
       <c r="R64" t="n">
-        <v>6832568</v>
+        <v>6832601</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6906,22 +6906,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708583</v>
+        <v>125708074</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,34 +6929,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495841</v>
+        <v>495733</v>
       </c>
       <c r="R65" t="n">
-        <v>6833181</v>
+        <v>6832780</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125708074</v>
+        <v>125708596</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7050,13 +7050,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495733</v>
+        <v>495930</v>
       </c>
       <c r="R66" t="n">
-        <v>6832780</v>
+        <v>6833128</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7100,22 +7100,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125708596</v>
+        <v>125706873</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495930</v>
+        <v>495718</v>
       </c>
       <c r="R67" t="n">
-        <v>6833128</v>
+        <v>6832621</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7197,22 +7197,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125706873</v>
+        <v>125708583</v>
       </c>
       <c r="B68" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,34 +7220,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495718</v>
+        <v>495841</v>
       </c>
       <c r="R68" t="n">
-        <v>6832621</v>
+        <v>6833181</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -2730,10 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125706788</v>
+        <v>125706777</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495756</v>
+        <v>495767</v>
       </c>
       <c r="R23" t="n">
-        <v>6832675</v>
+        <v>6832677</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125706777</v>
+        <v>125706788</v>
       </c>
       <c r="B24" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495767</v>
+        <v>495756</v>
       </c>
       <c r="R24" t="n">
-        <v>6832677</v>
+        <v>6832675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125706637</v>
+        <v>125708014</v>
       </c>
       <c r="B33" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495737</v>
+        <v>495817</v>
       </c>
       <c r="R33" t="n">
-        <v>6832680</v>
+        <v>6832682</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3812,22 +3812,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125708848</v>
+        <v>125706538</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495680</v>
+        <v>495769</v>
       </c>
       <c r="R34" t="n">
-        <v>6832870</v>
+        <v>6832671</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125708014</v>
+        <v>125706637</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3932,21 +3932,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495817</v>
+        <v>495737</v>
       </c>
       <c r="R35" t="n">
-        <v>6832682</v>
+        <v>6832680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4006,22 +4006,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125706538</v>
+        <v>125708848</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4029,21 +4029,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495769</v>
+        <v>495680</v>
       </c>
       <c r="R36" t="n">
-        <v>6832671</v>
+        <v>6832870</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,48 +4115,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125706917</v>
+        <v>125707003</v>
       </c>
       <c r="B37" t="n">
-        <v>79009</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495776</v>
+        <v>495724</v>
       </c>
       <c r="R37" t="n">
-        <v>6832649</v>
+        <v>6832599</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4200,19 +4209,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125706947</v>
+        <v>125706917</v>
       </c>
       <c r="B38" t="n">
         <v>79009</v>
@@ -4247,10 +4256,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495763</v>
+        <v>495776</v>
       </c>
       <c r="R38" t="n">
-        <v>6832629</v>
+        <v>6832649</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,10 +4318,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125707384</v>
+        <v>125706947</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4320,21 +4329,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4344,13 +4353,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495765</v>
+        <v>495763</v>
       </c>
       <c r="R39" t="n">
-        <v>6832558</v>
+        <v>6832629</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4394,66 +4403,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707003</v>
+        <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495724</v>
+        <v>495765</v>
       </c>
       <c r="R40" t="n">
-        <v>6832599</v>
+        <v>6832558</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125706872</v>
+        <v>125706913</v>
       </c>
       <c r="B5" t="n">
-        <v>79009</v>
+        <v>92532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495765</v>
+        <v>495727</v>
       </c>
       <c r="R5" t="n">
-        <v>6832663</v>
+        <v>6832609</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125706791</v>
+        <v>125706872</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495730</v>
+        <v>495765</v>
       </c>
       <c r="R6" t="n">
-        <v>6832652</v>
+        <v>6832663</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125706913</v>
+        <v>125706791</v>
       </c>
       <c r="B7" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495727</v>
+        <v>495730</v>
       </c>
       <c r="R7" t="n">
-        <v>6832609</v>
+        <v>6832652</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125706524</v>
+        <v>125707511</v>
       </c>
       <c r="B9" t="n">
-        <v>79009</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495786</v>
+        <v>495780</v>
       </c>
       <c r="R9" t="n">
-        <v>6832670</v>
+        <v>6832481</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125707173</v>
+        <v>125706635</v>
       </c>
       <c r="B10" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495761</v>
+        <v>495776</v>
       </c>
       <c r="R10" t="n">
-        <v>6832581</v>
+        <v>6832691</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125706635</v>
+        <v>125706524</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495776</v>
+        <v>495786</v>
       </c>
       <c r="R11" t="n">
-        <v>6832691</v>
+        <v>6832670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125707511</v>
+        <v>125707173</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>79009</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495780</v>
+        <v>495761</v>
       </c>
       <c r="R12" t="n">
-        <v>6832481</v>
+        <v>6832581</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
         <v>125708132</v>
       </c>
       <c r="B13" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>125708060</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,48 +2730,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125706777</v>
+        <v>125707033</v>
       </c>
       <c r="B23" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495767</v>
+        <v>495733</v>
       </c>
       <c r="R23" t="n">
-        <v>6832677</v>
+        <v>6832598</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2815,22 +2824,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125706788</v>
+        <v>125706777</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2838,21 +2847,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2871,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495756</v>
+        <v>495767</v>
       </c>
       <c r="R24" t="n">
-        <v>6832675</v>
+        <v>6832677</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125707543</v>
+        <v>125706788</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2935,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2959,13 +2968,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495772</v>
+        <v>495756</v>
       </c>
       <c r="R25" t="n">
-        <v>6832482</v>
+        <v>6832675</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3009,66 +3018,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125707033</v>
+        <v>125707543</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495733</v>
+        <v>495772</v>
       </c>
       <c r="R26" t="n">
-        <v>6832598</v>
+        <v>6832482</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3227,7 +3227,7 @@
         <v>125706444</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,54 +3321,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125706445</v>
+        <v>125707016</v>
       </c>
       <c r="B29" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495778</v>
+        <v>495749</v>
       </c>
       <c r="R29" t="n">
-        <v>6832690</v>
+        <v>6832629</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,54 +3418,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125708314</v>
+        <v>125707083</v>
       </c>
       <c r="B30" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495700</v>
+        <v>495751</v>
       </c>
       <c r="R30" t="n">
-        <v>6832875</v>
+        <v>6832612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125707016</v>
+        <v>125706637</v>
       </c>
       <c r="B31" t="n">
-        <v>79009</v>
+        <v>80080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,21 +3526,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,13 +3550,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495749</v>
+        <v>495737</v>
       </c>
       <c r="R31" t="n">
-        <v>6832629</v>
+        <v>6832680</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3618,22 +3600,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125707083</v>
+        <v>125708014</v>
       </c>
       <c r="B32" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,21 +3623,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495751</v>
+        <v>495817</v>
       </c>
       <c r="R32" t="n">
-        <v>6832612</v>
+        <v>6832682</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,7 +3709,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125708014</v>
+        <v>125706538</v>
       </c>
       <c r="B33" t="n">
         <v>78977</v>
@@ -3762,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495817</v>
+        <v>495769</v>
       </c>
       <c r="R33" t="n">
-        <v>6832682</v>
+        <v>6832671</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3806,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125706538</v>
+        <v>125708848</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3817,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495769</v>
+        <v>495680</v>
       </c>
       <c r="R34" t="n">
-        <v>6832671</v>
+        <v>6832870</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,48 +3903,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125706637</v>
+        <v>125708314</v>
       </c>
       <c r="B35" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495737</v>
+        <v>495700</v>
       </c>
       <c r="R35" t="n">
-        <v>6832680</v>
+        <v>6832875</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4006,57 +3997,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125708848</v>
+        <v>125706445</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495680</v>
+        <v>495778</v>
       </c>
       <c r="R36" t="n">
-        <v>6832870</v>
+        <v>6832690</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,54 +4115,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125707003</v>
+        <v>125707384</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495724</v>
+        <v>495765</v>
       </c>
       <c r="R37" t="n">
-        <v>6832599</v>
+        <v>6832558</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4415,45 +4406,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707384</v>
+        <v>125707003</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495765</v>
+        <v>495724</v>
       </c>
       <c r="R40" t="n">
-        <v>6832558</v>
+        <v>6832599</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4515,7 +4515,7 @@
         <v>125706714</v>
       </c>
       <c r="B41" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125707372</v>
+        <v>125706892</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495764</v>
+        <v>495711</v>
       </c>
       <c r="R42" t="n">
-        <v>6832553</v>
+        <v>6832636</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4715,32 +4715,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125706691</v>
+        <v>125707372</v>
       </c>
       <c r="B43" t="n">
-        <v>79001</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4750,13 +4750,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495777</v>
+        <v>495764</v>
       </c>
       <c r="R43" t="n">
-        <v>6832671</v>
+        <v>6832553</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4800,44 +4800,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125706892</v>
+        <v>125706691</v>
       </c>
       <c r="B44" t="n">
-        <v>80080</v>
+        <v>79001</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4847,13 +4847,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495711</v>
+        <v>495777</v>
       </c>
       <c r="R44" t="n">
-        <v>6832636</v>
+        <v>6832671</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4897,60 +4897,75 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125706720</v>
+        <v>125707718</v>
       </c>
       <c r="B45" t="n">
-        <v>79009</v>
+        <v>56848</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495782</v>
+        <v>495818</v>
       </c>
       <c r="R45" t="n">
-        <v>6832661</v>
+        <v>6832436</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4994,60 +5009,54 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125707718</v>
+        <v>125708266</v>
       </c>
       <c r="B46" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5056,13 +5065,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495818</v>
+        <v>495706</v>
       </c>
       <c r="R46" t="n">
-        <v>6832436</v>
+        <v>6832880</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5106,66 +5115,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708266</v>
+        <v>125706720</v>
       </c>
       <c r="B47" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495706</v>
+        <v>495782</v>
       </c>
       <c r="R47" t="n">
-        <v>6832880</v>
+        <v>6832661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>125707720</v>
       </c>
       <c r="B51" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125706764</v>
+        <v>125706943</v>
       </c>
       <c r="B52" t="n">
-        <v>79009</v>
+        <v>80080</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495761</v>
+        <v>495715</v>
       </c>
       <c r="R52" t="n">
-        <v>6832671</v>
+        <v>6832599</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5706,44 +5706,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125707134</v>
+        <v>125708210</v>
       </c>
       <c r="B53" t="n">
-        <v>56963</v>
+        <v>80080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5753,13 +5753,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495770</v>
+        <v>495705</v>
       </c>
       <c r="R53" t="n">
-        <v>6832555</v>
+        <v>6832884</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5803,22 +5803,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125708210</v>
+        <v>125706764</v>
       </c>
       <c r="B54" t="n">
-        <v>80080</v>
+        <v>79009</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,21 +5826,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495705</v>
+        <v>495761</v>
       </c>
       <c r="R54" t="n">
-        <v>6832884</v>
+        <v>6832671</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125706943</v>
+        <v>125708307</v>
       </c>
       <c r="B55" t="n">
         <v>80080</v>
@@ -5947,10 +5947,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495715</v>
+        <v>495712</v>
       </c>
       <c r="R55" t="n">
-        <v>6832599</v>
+        <v>6832874</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6009,32 +6009,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125708307</v>
+        <v>125707134</v>
       </c>
       <c r="B56" t="n">
-        <v>80080</v>
+        <v>56963</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6044,10 +6044,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495712</v>
+        <v>495770</v>
       </c>
       <c r="R56" t="n">
-        <v>6832874</v>
+        <v>6832555</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125706779</v>
+        <v>125707479</v>
       </c>
       <c r="B57" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495724</v>
+        <v>495776</v>
       </c>
       <c r="R57" t="n">
-        <v>6832662</v>
+        <v>6832485</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6212,10 +6212,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125707479</v>
+        <v>125706779</v>
       </c>
       <c r="B58" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495776</v>
+        <v>495724</v>
       </c>
       <c r="R58" t="n">
-        <v>6832485</v>
+        <v>6832662</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6415,54 +6415,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125707493</v>
+        <v>125707093</v>
       </c>
       <c r="B60" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495766</v>
+        <v>495727</v>
       </c>
       <c r="R60" t="n">
-        <v>6832499</v>
+        <v>6832581</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6521,45 +6512,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125707093</v>
+        <v>125707493</v>
       </c>
       <c r="B61" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495727</v>
+        <v>495766</v>
       </c>
       <c r="R61" t="n">
-        <v>6832581</v>
+        <v>6832499</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6815,7 +6815,7 @@
         <v>125707073</v>
       </c>
       <c r="B64" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125708074</v>
+        <v>125706873</v>
       </c>
       <c r="B65" t="n">
         <v>80080</v>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>495733</v>
+        <v>495718</v>
       </c>
       <c r="R65" t="n">
-        <v>6832780</v>
+        <v>6832621</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125708596</v>
+        <v>125708583</v>
       </c>
       <c r="B66" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7026,37 +7026,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>495930</v>
+        <v>495841</v>
       </c>
       <c r="R66" t="n">
-        <v>6833128</v>
+        <v>6833181</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7100,19 +7100,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125706873</v>
+        <v>125708074</v>
       </c>
       <c r="B67" t="n">
         <v>80080</v>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495718</v>
+        <v>495733</v>
       </c>
       <c r="R67" t="n">
-        <v>6832621</v>
+        <v>6832780</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125708583</v>
+        <v>125708596</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7220,37 +7220,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gässtjärnen, Gässtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495841</v>
+        <v>495930</v>
       </c>
       <c r="R68" t="n">
-        <v>6833181</v>
+        <v>6833128</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7294,12 +7294,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 20959-2025 artfynd.xlsx
+++ b/artfynd/A 20959-2025 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125707511</v>
+        <v>125706524</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>79009</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495780</v>
+        <v>495786</v>
       </c>
       <c r="R9" t="n">
-        <v>6832481</v>
+        <v>6832670</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125706635</v>
+        <v>125707173</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495776</v>
+        <v>495761</v>
       </c>
       <c r="R10" t="n">
-        <v>6832691</v>
+        <v>6832581</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,48 +1548,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125706524</v>
+        <v>125708132</v>
       </c>
       <c r="B11" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495786</v>
+        <v>495728</v>
       </c>
       <c r="R11" t="n">
-        <v>6832670</v>
+        <v>6832782</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1642,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125707173</v>
+        <v>125707511</v>
       </c>
       <c r="B12" t="n">
-        <v>79009</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1689,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495761</v>
+        <v>495780</v>
       </c>
       <c r="R12" t="n">
-        <v>6832581</v>
+        <v>6832481</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,69 +1739,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125708132</v>
+        <v>125706635</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495728</v>
+        <v>495776</v>
       </c>
       <c r="R13" t="n">
-        <v>6832782</v>
+        <v>6832691</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -4115,45 +4115,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125707384</v>
+        <v>125707003</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495765</v>
+        <v>495724</v>
       </c>
       <c r="R37" t="n">
-        <v>6832558</v>
+        <v>6832599</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4406,54 +4415,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125707003</v>
+        <v>125707384</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495724</v>
+        <v>495765</v>
       </c>
       <c r="R40" t="n">
-        <v>6832599</v>
+        <v>6832558</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5621,45 +5621,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125706943</v>
+        <v>125706779</v>
       </c>
       <c r="B52" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495715</v>
+        <v>495724</v>
       </c>
       <c r="R52" t="n">
-        <v>6832599</v>
+        <v>6832662</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5718,10 +5727,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125708210</v>
+        <v>125706764</v>
       </c>
       <c r="B53" t="n">
-        <v>80080</v>
+        <v>79009</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5729,21 +5738,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5753,10 +5762,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495705</v>
+        <v>495761</v>
       </c>
       <c r="R53" t="n">
-        <v>6832884</v>
+        <v>6832671</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5815,10 +5824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125706764</v>
+        <v>125708307</v>
       </c>
       <c r="B54" t="n">
-        <v>79009</v>
+        <v>80080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,21 +5835,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5850,13 +5859,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495761</v>
+        <v>495712</v>
       </c>
       <c r="R54" t="n">
-        <v>6832671</v>
+        <v>6832874</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5900,19 +5909,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125708307</v>
+        <v>125706943</v>
       </c>
       <c r="B55" t="n">
         <v>80080</v>
@@ -5947,10 +5956,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495712</v>
+        <v>495715</v>
       </c>
       <c r="R55" t="n">
-        <v>6832874</v>
+        <v>6832599</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6009,32 +6018,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125707134</v>
+        <v>125708210</v>
       </c>
       <c r="B56" t="n">
-        <v>56963</v>
+        <v>80080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6044,13 +6053,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495770</v>
+        <v>495705</v>
       </c>
       <c r="R56" t="n">
-        <v>6832555</v>
+        <v>6832884</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6094,66 +6103,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125707479</v>
+        <v>125707134</v>
       </c>
       <c r="B57" t="n">
-        <v>98352</v>
+        <v>56963</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495776</v>
+        <v>495770</v>
       </c>
       <c r="R57" t="n">
-        <v>6832485</v>
+        <v>6832555</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125706779</v>
+        <v>125707479</v>
       </c>
       <c r="B58" t="n">
         <v>98352</v>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495724</v>
+        <v>495776</v>
       </c>
       <c r="R58" t="n">
-        <v>6832662</v>
+        <v>6832485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6618,48 +6618,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125707370</v>
+        <v>125707073</v>
       </c>
       <c r="B62" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495793</v>
+        <v>495738</v>
       </c>
       <c r="R62" t="n">
-        <v>6832568</v>
+        <v>6832601</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6703,22 +6712,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125706395</v>
+        <v>125707370</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6735,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495818</v>
+        <v>495793</v>
       </c>
       <c r="R63" t="n">
-        <v>6832725</v>
+        <v>6832568</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6800,69 +6809,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125707073</v>
+        <v>125706395</v>
       </c>
       <c r="B64" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>495738</v>
+        <v>495818</v>
       </c>
       <c r="R64" t="n">
-        <v>6832601</v>
+        <v>6832725</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
